--- a/code/experiment/512chunk_BGE-M3-5topk_Y.xlsx
+++ b/code/experiment/512chunk_BGE-M3-5topk_Y.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rag_project\code\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rag_project\code\experiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F4033CB-CBFF-4610-AD68-029387DA631B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9309F8E4-B59B-4152-BA6A-D8AD1D193924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="13770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -80,57 +80,31 @@
     <t>is_correct_refusal</t>
   </si>
   <si>
-    <t>在论文"A Survey of Post-Training Scaling in Large Language Models"中，作者将post-training scaling分为哪三个主要方法？</t>
-  </si>
-  <si>
     <t>定义类</t>
   </si>
   <si>
     <t>作者将post-training scaling分为三个主要方法：Supervised Fine-tuning (SFT), Reinforcement Learning (RLxF), and Test-time Compute (TTC).</t>
   </si>
   <si>
-    <t>作者将post-training scaling分为三个主要方法：Supervised Fine-tuning（监督微调）、Reinforcement Learning（强化学习）和Test-time Compute（测试时计算）。
-来自: [2025.acl-long.140_A Survey of Post-Training Scaling in Large Language Models, 第2页, 2025.acl-long.140_A Survey of Post-Training Scaling in Large Language Models_chunk_005]</t>
-  </si>
-  <si>
     <t>在SafeRAG中"silver noise"的定义是什么？</t>
   </si>
   <si>
     <t>首先，我们定义了“银色噪声”，它指的是仅部分包含答案的证据文本。此类噪声能够绕过大多数安全过滤机制，从而削弱 RAG 的多样性。</t>
   </si>
   <si>
-    <t>在SafeRAG中，"silver noise"是指包含部分但不完整答案的噪声。
-来自: [2025.acl-long.230_SafeRAG, 第4页, 2025.acl-long.230_SafeRAG_chunk_009]</t>
-  </si>
-  <si>
-    <t>RAG噪声被分为哪两类？</t>
-  </si>
-  <si>
     <t>RAG噪声被分为有益噪声和有害噪声。</t>
   </si>
   <si>
-    <t>RAG噪声被分为有益噪声（beneficial noise）和有害噪声（harmful noise）两类。
-来自: [2025.acl-long.250_Pandora s Box or Aladdin s Lamp, 第2页, 2025.acl-long.250_Pandora s Box or Aladdin s Lamp_chunk_005]</t>
-  </si>
-  <si>
     <t>什么是Ref-Long基准？它评估的是长上下文语言模型的什么能力？</t>
   </si>
   <si>
     <t>Ref-Long是一个专门设计用于评估长上下文语言模型（LCLMs）长上下文引用能力的基准。它要求LCLMs不仅要在给定文档中识别特定关键词，还要找出引用该关键词的文档索引，而不是其他相关但不匹配的文档。</t>
   </si>
   <si>
-    <t>Ref-Long（Referencing Evaluation for Long-context Language Models）是一个专为评估长上下文语言模型（LCLMs）的长上下文引用能力而设计的新基准。它要求模型在给定多个索引文档和一个查询时，不仅检索出特定的键，还要识别出所有引用该键的文档索引，从而考察模型对键与上下文关系的真正理解，而非简单的检索。
-来自: [2025.acl-long.1162_Ref-Long, 第1页, 2025.acl-long.1162_Ref-Long_chunk_000] 和 [2025.acl-long.1162_Ref-Long, 第1页, 2025.acl-long.1162_Ref-Long_chunk_001]</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 什么是SYNQA方法？</t>
   </si>
   <si>
     <t>SYNQA 是一种生成式上下文归因数据合成方法。核心思路是：给定选定的上下文句子，由大语言模型（LLM）生成完全受这些句子支持的问题-答案对（QA对）。该方法能够产生反映真实世界多样化问答场景的训练数据，帮助模型学习稳健的归因能力。SYNQA 同时生成以实体为中心和以对话为中心的样本，从而提升模型在不同上下文和领域的泛化能力。</t>
-  </si>
-  <si>
-    <t>SYNQA是一种生成式策略，通过给定上下文句子让大语言模型生成受其支持的问题-答案对来合成上下文归因数据。
-来自: [2025.acl-long.828_On Synthesizing Data for Context Attribution in Question Answering, 第1页, 2025.acl-long.828_On Synthesizing Data for Context Attribution in Question Answering_chunk_001]</t>
   </si>
   <si>
     <t>什么是Agentic Long-Context Understanding (AgenticLU)框架？</t>
@@ -140,84 +114,46 @@
 </t>
   </si>
   <si>
-    <t>AgenticLU是一个旨在通过将有针对性的自我澄清与上下文 grounding 集成到智能体工作流中，增强大语言模型对长上下文查询理解的框架。
-来自: [2025.acl-long.275_Self-Taught Agentic Long Context Understanding, 第1页, 2025.acl-long.275_Self-Taught Agentic Long Context Understanding_chunk_000]</t>
-  </si>
-  <si>
     <t>什么是Agentic Reasoning框架?</t>
   </si>
   <si>
     <t>Agentic Reasoning是一个通过集成外部工具使用代理来增强大型语言模型推理的框架。</t>
   </si>
   <si>
-    <t>Agentic Reasoning是一个通过集成外部基于LLM的代理作为工具来增强推理的框架，允许LLM在推理过程中将特定任务委托给辅助代理。
-来自: [2025.acl-long.1383_Agentic Reasoning, 第2页, 2025.acl-long.1383_Agentic Reasoning_chunk_003]</t>
-  </si>
-  <si>
     <t>REAL-MM-RAG 基准测试旨在解决现实世界检索的四个关键属性是什么？</t>
   </si>
   <si>
     <t xml:space="preserve"> REAL-MM-RAG基准测试的四个关键属性是：(i) 多模态文档，(ii) 增强的难度，(iii) 真实的RAG查询，(iv) 准确的标注。</t>
   </si>
   <si>
-    <t>REAL-MM-RAG 基准测试旨在解决的四个关键属性是：(i) 多模态文档，(ii) 增强的难度，(iii) 真实 RAG 查询，以及 (iv) 准确的标注。
-来自: [2025.acl-long.1528_REAL-MM-RAG, 第1页, 2025.acl-long.1528_REAL-MM-RAG_chunk_000]</t>
-  </si>
-  <si>
     <t>ASTUTE RAG的定义是什么？有什么用?</t>
   </si>
   <si>
     <t>为了使大语言模型对不完美的检索结果更具鲁棒性，我们提出了 ASTUTE RAG，这是一种新颖的检索增强生成方法。该方法能够自适应地从大语言模型的内部知识中提取关键信息，在感知信息来源的基础上迭代整合内外部知识，并根据信息的可靠性最终生成答案。</t>
   </si>
   <si>
-    <t>ASTUTE RAG是一种新颖的RAG方法，旨在对不完美的检索增强具有弹性，同时在检索可靠时保留RAG的接地效果。它用于有效区分LLM内部知识与外部检索段落中的一致和冲突信息，评估其可靠性，并确保可信信息的正确整合，从而缓解知识冲突并提高响应的鲁棒性。
-来自: [2025.acl-long.1476_Astute RAG, 第2页, 2025.acl-long.1476_Astute RAG_chunk_004]</t>
-  </si>
-  <si>
     <t>L-CiteEval的定义是什么？</t>
   </si>
   <si>
     <t>L-CiteEval是一个开箱即用的评估套件，用于评估长上下文模型（LCMs）的生成质量和保真度。它包含两个关键组件：（1）一个涵盖5大任务类别和11个多样化长上下文任务的综合基准测试，上下文长度从8K到48K；（2）相应的自动评估指标和验证流程，以确保稳健可靠的评估。该套件要求模型生成陈述及其支持证据（引用），从而能够有效区分不同模型在保真度方面的差异。</t>
   </si>
   <si>
-    <t>L-CiteEval是一个开箱即用的评估套件，用于评估长上下文模型在长上下文理解任务中的生成质量和忠实度。
-来自: [2025.acl-long.263_L-CiteEval, 第1页, 2025.acl-long.263_L-CiteEval_chunk_000]</t>
-  </si>
-  <si>
     <t xml:space="preserve"> LongBench v2基准测试包含多少个问题？上下文长度范围是多少？</t>
   </si>
   <si>
     <t>LongBench v2包含503个具有挑战性的多项选择题，上下文长度范围从8,000到200万个单词。</t>
   </si>
   <si>
-    <t>LongBench v2基准测试包含503个多项选择题，上下文长度范围从8k到2M words。
-来自: [2025.acl-long.183_LongBench v2, 第1页, 2025.acl-long.183_LongBench v2_chunk_002]</t>
-  </si>
-  <si>
     <t>RHIO框架的三个主要组成部分是什么？</t>
   </si>
   <si>
     <t>RHIO框架包含三个主要组件：1.不忠实数据增强, 2.忠实度感知调优, 3.自诱导解码</t>
   </si>
   <si>
-    <t>RHIO框架的三个主要组成部分是：不忠实数据增强（Unfaithful Data Augmentation）、忠实性感知微调（Faithfulness-Aware Tuning）和自我诱导解码（Self-Induced Decoding）。
-来自: [2025.acl-long.826_Improving Contextual Faithfulness of Large Language Models via Retrieval Heads-Induced Optimization, 第15页, 2025.acl-long.826_Improving Contextual Faithfulness of Large Language Models via Retrieval Heads-Induced Optimization_chunk_030]</t>
-  </si>
-  <si>
-    <t>在How to Train Long-Context Language Models中的监督微调（SFT）阶段，论文作者发现使用哪种类型的数据集能够在长上下文任务上取得最佳性能？</t>
-  </si>
-  <si>
     <t>方法细节类</t>
   </si>
   <si>
     <t>作者发现，仅使用标准的、短上下文的指令数据集（如 UltraChat）进行微调，就能在长上下文任务上取得最佳效果。</t>
-  </si>
-  <si>
-    <t>作者发现，使用标准的短上下文指令数据集（standard, short-context instruction datasets）进行监督微调即可在长上下文任务上取得最佳性能，而长合成指令数据并未带来进一步提升。
-来自: [2025.acl-long.366_How to Train Long-Context Language Models (Effectively), 第1页, 2025.acl-long.366_How to Train Long-Context Language Models (Effectively)_chunk_002]</t>
-  </si>
-  <si>
-    <t>在"Astute RAG"中，作者提出的knowledge consolidation过程包含哪三个主要步骤？</t>
   </si>
   <si>
     <t>Knowledge Consolidation（知识整合）过程包含以下三个主要步骤：
@@ -226,38 +162,19 @@
 过滤无关信息：剔除与当前查询或任务不相关的冗余内容。</t>
   </si>
   <si>
-    <t>knowledge consolidation过程包含三个主要步骤：识别跨段落的一致信息、检测一致信息组之间的冲突信息、过滤无关信息。
-来自: [2025.acl-long.1476_Astute RAG, 第5页, 2025.acl-long.1476_Astute RAG_chunk_011]</t>
-  </si>
-  <si>
-    <t>LongRefiner 在推理时如何降低在线延迟？</t>
-  </si>
-  <si>
     <t>将推理分为离线阶段和在线阶段。离线阶段完成文档结构化任务，在线阶段仅处理用户查询分析和自适应精炼（输入输出仅数百个 tokens），整体延迟约为标准设置的 25%。</t>
   </si>
   <si>
-    <t>LongRefiner 将推理过程拆分为离线和在线两个阶段：离线阶段预先对语料库中的文档执行层次化文档结构化任务，在线阶段仅需对用户查询进行分析并执行自适应精炼以生成最终输出。由于在线阶段只需处理数百个输入 token 并生成数十个输出 token，整体延迟仅为标准设置的约 25%。
-来自: [2025.acl-long.176_Hierarchical Document Refinement for Long-context Retrieval-augmented Generation, 第6页, 2025.acl-long.176_Hierarchical Document Refinement for Long-context Retrieval-augmented Generation_chunk_013]</t>
-  </si>
-  <si>
     <t>DRAG框架如何保护用户隐私？请描述其隐私保护机制。</t>
   </si>
   <si>
     <t>DRAG通过传输去标识化的查询和结构化知识而不是完整响应来保护用户隐私。这样可以避免传输完整的用户查询和敏感信息。</t>
   </si>
   <si>
-    <t>DRAG框架通过本地小模型对用户查询进行改写，剥离敏感信息后发送至云端大模型，云端仅返回证据和知识图谱，再由本地模型生成最终答案，从而避免用户隐私数据上传至云端。
-来自: [2025.acl-long.358_DRAG, 第5页, 2025.acl-long.358_DRAG_chunk_010] 和 [2025.acl-long.358_DRAG, 第1页, 2025.acl-long.358_DRAG_chunk_001]</t>
-  </si>
-  <si>
     <t>简述 Think&amp; Cite 框架中 SG-MCTS 的工作流程及其步骤。</t>
   </si>
   <si>
     <t>SG-MCTS利用LLMs的自反思能力来推理MCTS的中间状态，以指导树扩展过程。在每次迭代中，SG-MCTS 遵循四个步骤，即选择、反思引导的扩展、评估和反向传播。</t>
-  </si>
-  <si>
-    <t>SG-MCTS（自引导蒙特卡洛树搜索）将归因文本生成视为多步推理问题，每次迭代包含四个步骤：**选择**（用UCT算法选出最优节点）、**反思引导的扩展**（通过“思考-表达-引用”范式生成下一句，并利用LLM的自我反思能力实时批评和优化中间状态，避免错误路径）、**评估**（用进度奖励模型从生成进度和归因进度两方面计算奖励）以及**反向传播**（将奖励沿路径回传更新节点值）。
-来自: [2025.acl-long.490_Think&amp;Cite, 第3页, 2025.acl-long.490_Think&amp;Cite_chunk_006]、[2025.acl-long.490_Think&amp;Cite, 第4页, 2025.acl-long.490_Think&amp;Cite_chunk_008]、[2025.acl-long.490_Think&amp;Cite, 第7页, 2025.acl-long.490_Think&amp;Cite_chunk_021]</t>
   </si>
   <si>
     <t>SETR 的段落选择提示（Passage Selection Prompt）所引导的关键过程包含哪三个具体步骤？每个步骤的核心任务是什么？</t>
@@ -269,211 +186,418 @@
 选择最优段落子集： 核心任务是从候选段落中挑选出一个子集，使其在整体上能提供最全面且多样化的信息覆盖，从而有效回答查询。</t>
   </si>
   <si>
+    <t>Meta-Bench基准测试中，α参数的最优范围是多少？这个参数的作用是什么？</t>
+  </si>
+  <si>
+    <t>α参数的最优范围在0.65到0.8之间。这个参数用于平衡工具描述和参数描述在工具检索中的权重。</t>
+  </si>
+  <si>
+    <t>CypherBench 是如何从 RDF 图生成领域特定属性图的？</t>
+  </si>
+  <si>
+    <t>CypherBench 通过将 RDF 图转换为多个领域特定的属性图（domain-specific property graphs）来实现这一过程，并使用 Cypher 语言对其进行查询。</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ClinRaGen框架的三阶段理由蒸馏范式是什么？</t>
+  </si>
+  <si>
+    <t>ClinRaGen框架采用三阶段理由蒸馏范式：第一阶段从医疗笔记中蒸馏理由，让SLM发展对文本临床信息的基础理解；第二阶段引入知识增强注意力，将数值实验室测试与结构化医学知识对齐，蒸馏实验室测试为基础的理由；第三阶段完全整合文本和数值输入，使SLM能够生成临床连贯的多模态理由以支持疾病诊断。</t>
+  </si>
+  <si>
+    <t>QAEncoder如何解决文档-查询差距问题？</t>
+  </si>
+  <si>
+    <t>QAEncoder采用了一种无需训练的方法来弥合文档与查询之间的差距。其核心机制包含两点：
+潜在查询期望估计： 在嵌入空间中估计潜在查询的期望值，将其作为文档嵌入的鲁棒替代表示，从而使文档表示在语义上更贴近查询空间。
+文档指纹附加： 为这些嵌入表示附加文档指纹，以有效区分不同文档的嵌入，避免仅依赖查询期望导致的文档辨识度丢失问题。</t>
+  </si>
+  <si>
+    <t>在 HALOGEN 的文本简化任务中，如何验证模型生成的简化文本是否忠实于原文？</t>
+  </si>
+  <si>
+    <t>先用 GPT-3.5-turbo 将简化文本分解为独立的原子事实，再用 Llama-2-70B-chat 判断每个原子事实是否被原文蕴含。</t>
+  </si>
+  <si>
+    <t>在"CiteEval"论文中，GPT-4o和Llama-3-70B在Cited scenario和Full scenario下的表现有何差异？</t>
+  </si>
+  <si>
+    <t>实验结果类</t>
+  </si>
+  <si>
+    <t>在Cited scenario下，GPT-4o表现最佳，Llama-3-70B与GPT-4o-mini相当；在Full scenario下，Llama-3-70B超越GPT-4o，取得最佳性能。</t>
+  </si>
+  <si>
+    <t>"FaithfulRAG"在FaithEval数据集上使用Mistral-7B作为backbone时的准确率是多少？相比最强基线提高了多少？</t>
+  </si>
+  <si>
+    <t>81.7%，比最强基线(KRE的73.2%)提高了8.5%。</t>
+  </si>
+  <si>
+    <t>RankCoT 相对于 vanilla RAG 模型的表现如何？这说明了什么？</t>
+  </si>
+  <si>
+    <t>RankCoT 相比 vanilla RAG 模型有 2.5% 的提升，表明它在提供更有意义的细化方面有效，有助于 LLM 更好地回答问题。</t>
+  </si>
+  <si>
+    <t>在 HALoGEN 基准测试中，表现最好的 LLM 生成事实的幻觉率范围是多少？</t>
+  </si>
+  <si>
+    <t>实验发现，即使是表现最好的 LLM，其生成事实的幻觉率也在 3% 到 86% 之间，具体数值取决于所属领域。</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 在LongBench v2基准测试中，人类专家在15分钟时间限制下的准确率是多少？</t>
+  </si>
+  <si>
+    <t>人类专家在15分钟时间限制下的准确率为53.7%。</t>
+  </si>
+  <si>
+    <t>AGENTSTAR方法在WebShop、ALFWorld和BabyAI任务上与GPT-4-Turbo相比有何优势？</t>
+  </si>
+  <si>
+    <t>AGENTSTAR 在这三个任务上的性能全面超越了 GPT-4-Turbo。其中在 WebShop 上的提升最为显著（远超 GPT-4-Turbo 61 个百分点），在 ALFWorld 和 BabyAI 上也分别实现了大幅领先（超过 GPT-4-Turbo 20.5 和 9.87 个百分点）。</t>
+  </si>
+  <si>
+    <t>在Humanity's Last Exam数据集上，Agentic Reasoning与DeepSeek-R1结合的性能提升是多少？与OpenAI Deep Research的差距如何变化？</t>
+  </si>
+  <si>
+    <t>在Humanity's Last Exam数据集上，Agentic Reasoning与DeepSeek-R1结合达到了23.8%的准确率，比基础模型提升了14.4%，与专有的OpenAI Deep Research的差距缩小到仅2.8%。</t>
+  </si>
+  <si>
+    <t>在GAIA基准测试中，Agentic Reasoning在不同级别任务上的表现如何？</t>
+  </si>
+  <si>
+    <t>在GAIA基准测试中，Agentic Reasoning在Level 1和Level 2任务上超越了OpenAI的Deep Research，在Level 3任务上将差距缩小到2.26%。</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 在Asclepius医学基准测试中，人类医生与Med-MLLMs的表现对比如何？</t>
+  </si>
+  <si>
+    <t>在Asclepius基准测试中，人类医生在所有专业领域都超过了Med-MLLMs。即使是平均准确率为57.4%的初级医生也略微超过了表现最好的Med-MLLM GPT-4V（准确率为54.3%）。这表明尽管人工智能取得了进步，但在诊断精度方面人类专业知识与当前Med-MLLMs之间仍存在差距。</t>
+  </si>
+  <si>
+    <t>在LongDocURL基准测试中，GPT-4o的表现如何？其他开源模型呢？</t>
+  </si>
+  <si>
+    <t>在LongDocURL基准测试中，只有GPT-4o达到了及格标准，得分为64.5，表明该基准对当前模型提出了重大挑战。在开源模型中，只有Qwen2-VL（得分30.6）和LLaVA-OneVision（得分22.0和25.0）超过了20分的阈值，其他参数少于13B的模型都低于这个阈值。</t>
+  </si>
+  <si>
+    <t>RAGEval 提出的自动评估指标与人工评估的一致性如何？</t>
+  </si>
+  <si>
+    <t>实验结果表明，RAGEval 的机器自动评估与人工评估在所有指标上均表现出高度一致性。两者之间的最终绝对差异仅为 1.67%。</t>
+  </si>
+  <si>
+    <t>在利用大模型内部知识应对知识冲突时，《Astute RAG》与《FaithfulRAG》各自采用了什么核心机制/模块来提取或生成内部知识？</t>
+  </si>
+  <si>
+    <t>跨论文比较类</t>
+  </si>
+  <si>
+    <t>《Astute RAG》：采用自适应段落生成机制，通过提示大模型直接生成包含内部知识的段落，并允许模型自适应决定生成的段落数量。
+《FaithfulRAG》：采用自我事实挖掘 模块，通过外部化大模型对问题的理解，提取出细粒度的、事实级别的内部知识。</t>
+  </si>
+  <si>
+    <t>"UniRAG"和"FaithfulRAG"在处理查询理解方面的核心创新分别是什么？</t>
+  </si>
+  <si>
+    <t>UniRAG提出统一的查询理解框架，集成查询增强和查询编码两个阶段；FaithfulRAG通过自我事实挖掘和自思考模块，在事实级别识别并解决参数化知识与检索上下文之间的冲突，提高语义一致性。</t>
+  </si>
+  <si>
+    <t>比较MEMERAG和DragonBall两个基准的异同点，它们各自关注的评估维度是什么？</t>
+  </si>
+  <si>
+    <t>相同点：两者都是多语言RAG评估基准。不同点：MEMERAG专注于多语言端到端元评估，使用母语问题并由专家评估忠实度和相关性；DragonBall是一个多场景多语言RAG全能基准，涵盖金融、法律、医疗领域，包含6,711个问题，用于评估RAG系统在不同场景下的性能。</t>
+  </si>
+  <si>
+    <t>SYNQA 和 RHIO 分别通过什么方式生成训练数据？这两种数据生成策略在提升模型归因能力上有什么不同？</t>
+  </si>
+  <si>
+    <t>SYNQA：通过 LLM 生成式合成完全受上下文支持的 QA 对（正样本），用于微调小模型的归因能力。
+RHIO：通过选择性掩码检索头，让 LLM 自身生成模拟真实错误的不忠实样本（负样本），并与忠实样本进行联合训练。</t>
+  </si>
+  <si>
+    <t>比较LongBench v2和AGENTGYM应用场景区别。</t>
+  </si>
+  <si>
+    <t>LongBench v2：专注于长上下文理解的多任务评估，包含503个多项选择题，上下文长度从8k到2M单词，涵盖6个主要任务类别，用于评估LLM在长文档理解和推理方面的能力
+AGENTGYM：专注于代理训练和工具使用的环境集合，包含11个不同的交互环境（如Minecraft、ScienceWorld、BabyAI等），用于训练和评估LLM代理在多样化任务中的能力</t>
+  </si>
+  <si>
+    <t>Agentic Reasoning 与 AR-MCTS 分别采用什么核心机制来提升复杂推理能力？</t>
+  </si>
+  <si>
+    <t>Agentic Reasoning：动态调用网页搜索、代码执行作为工具，并引入 Mind‑Map 知识图谱智能体作为结构化记忆，存储推理上下文并追踪逻辑关系。
+AR-MCTS：基于蒙特卡洛树搜索（MCTS），在扩展阶段集成主动检索（Active Retrieval） 机制，自动获取逐步推理的高质量标注，渐进式提升多模态大模型的推理能力。</t>
+  </si>
+  <si>
+    <t>MAIN‑RAG 与 RAG‑Critic 在提升 RAG 系统可靠性方面分别采用了什么核心方法？</t>
+  </si>
+  <si>
+    <t>MAIN‑RAG 采用多智能体协作过滤机制，通过三个 LLM 智能体（Predictor、Judge、Final‑Predictor）对检索文档进行相关性评分和排序，并利用自适应阈值动态过滤噪声文档，无需训练。
+RAG‑Critic 采用批评引导的智能体工作流，首先构建层次化 RAG 错误系统（3 级错误类型，含 4000+ 细粒度标签），然后训练轻量级错误批评模型进行自动错误诊断，最后通过规划智能体根据错误反馈定制并执行修正方案。</t>
+  </si>
+  <si>
+    <t>MAIN‑RAG 采用训练无关的多智能体协同过滤与自适应阈值机制，通过多个 LLM 智能体对检索文档进行评分和筛选，动态调整相关性阈值以降低噪声。RAG‑Critic 则构建数据驱动的层次化错误体系，训练错误批评模型，并利用批评引导的智能体工作流进行错误驱动的纠正，自动定制解决方案流程。
+来自: [2025.acl-long.131_MAIN-RAG, 第1页, 2025.acl-long.131_MAIN-RAG_chunk_004] 来自: [2025.acl-long.179_RAG-Critic, 第9页, 2025.acl-long.179_RAG-Critic_chunk_020]</t>
+  </si>
+  <si>
+    <t>在构建可靠的问答（QA）系统时，这QAEncoder与On Synthesizing Data for Context Attribution in Question Answering两篇论文分别侧重于优化系统工作流的哪个阶段？它们各自试图解决的核心痛点是什么？</t>
+  </si>
+  <si>
+    <t>《QAEncoder》侧重于“检索阶段”
+核心痛点：用户的自然语言查询与知识库中的文档之间存在语义和词汇上的鸿沟，导致检索模块无法精准召回相关文档。
+《On Synthesizing Data for Context Attribution... (SYNQA)》侧重于“生成后阶段”
+核心痛点：大语言模型在生成答案时容易产生幻觉，用户很难验证生成的答案是否真的基于提供的上下文，缺乏可解释性和事实依据。</t>
+  </si>
+  <si>
+    <t>这10篇论文中哪一篇提出了名为"RAG-Guard"的安全防护框架？</t>
+  </si>
+  <si>
+    <t>不可回答类</t>
+  </si>
+  <si>
+    <t>无法回答。</t>
+  </si>
+  <si>
+    <t>根据已有信息，无法回答此问题。</t>
+  </si>
+  <si>
+    <t>"ProLong"模型在训练过程中使用了哪种具体的优化器来处理长序列训练的梯度问题？</t>
+  </si>
+  <si>
+    <t>SETR模型在训练时具体的训练时间是多少小时？</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> L-CiteEval基准中使用的NLI模型deberta-base-long-nli的准确率是多少？该模型在哪些具体数据集上进行了训练？</t>
+  </si>
+  <si>
+    <t>论文中是否提到了SYNQA方法在医疗领域的具体应用案例？</t>
+  </si>
+  <si>
+    <t>论文中是否提供了RHIO方法在实时应用场景中的延迟测试数据？</t>
+  </si>
+  <si>
+    <t>Agentic Reasoning框架中使用的Mind-Map agent的具体神经网络架构是什么？</t>
+  </si>
+  <si>
+    <t>在CypherBench基准测试中，每个问题模板具体包含多少个训练样本？</t>
+  </si>
+  <si>
+    <t>【总体平均值】</t>
+  </si>
+  <si>
+    <t>【定义类平均值】</t>
+  </si>
+  <si>
+    <t>【方法细节类平均值】</t>
+  </si>
+  <si>
+    <t>【实验结果类平均值】</t>
+  </si>
+  <si>
+    <t>【跨论文比较类平均值】</t>
+  </si>
+  <si>
+    <t>【不可回答类平均值】</t>
+  </si>
+  <si>
+    <t>在论文"A Survey of Post-Training Scaling in Large Language Models"中，作者将post-training scaling分为哪三个主要方法？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RAG噪声被分为哪两类？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在"Astute RAG"中，作者提出的knowledge consolidation过程包含哪三个主要步骤？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LongRefiner 在推理时如何降低在线延迟？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在How to Train Long-Context Language Models中的监督微调（SFT）阶段，论文作者发现使用哪种类型的数据集能够在长上下文任务上取得最佳性能？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>作者将post-training scaling分为三个主要方法：Supervised Fine-tuning（监督微调）、Reinforcement Learning（强化学习）和Test-time Compute（测试时计算）。
+来自: [A Survey of Post-Training Scaling in Large Language Models, 第2页, A Survey of Post-Training Scaling in Large Language Models_chunk_005]</t>
+  </si>
+  <si>
+    <t>在SafeRAG中，"silver noise"是指包含部分但不完整答案的噪声。
+来自: [SafeRAG: Benchmarking Security in Retrieval-Augmented Generation of Large Language Model, 第4页, SafeRAG: Benchmarking Security in Retrieval-Augmented Generation of Large Language Model_chunk_009]</t>
+  </si>
+  <si>
+    <t>RAG噪声被分为有益噪声（beneficial noise）和有害噪声（harmful noise）两类。
+来自: [Pandora’s Box or Aladdin’s Lamp: A Comprehensive Analysis Revealing the Role of RAG Noise in Large Language Models, 第2页, Pandora’s Box or Aladdin’s Lamp: A Comprehensive Analysis Revealing the Role of RAG Noise in Large Language Models_chunk_005]</t>
+  </si>
+  <si>
+    <t>Ref-Long（Referencing Evaluation for Long-context Language Models）是一个专为评估长上下文语言模型（LCLMs）的长上下文引用能力而设计的新基准。它要求模型在给定多个索引文档和一个查询时，不仅检索出特定的键，还要识别出所有引用该键的文档索引，从而考察模型对键与上下文关系的真正理解，而非简单的检索。
+来自: [Ref-Long: Benchmarking the Long-context Referencing Capability of Long-context Language Models, 第1页, Ref-Long: Benchmarking the Long-context Referencing Capability of Long-context Language Models_chunk_000] 和 [Ref-Long: Benchmarking the Long-context Referencing Capability of Long-context Language Models, 第1页, Ref-Long: Benchmarking the Long-context Referencing Capability of Long-context Language Models_chunk_001]</t>
+  </si>
+  <si>
+    <t>SYNQA是一种生成式策略，通过给定上下文句子让大语言模型生成受其支持的问题-答案对来合成上下文归因数据。
+来自: [On Synthesizing Data for Context Attribution in Question Answering, 第1页, On Synthesizing Data for Context Attribution in Question Answering_chunk_001]</t>
+  </si>
+  <si>
+    <t>AgenticLU是一个旨在通过将有针对性的自我澄清与上下文 grounding 集成到智能体工作流中，增强大语言模型对长上下文查询理解的框架。
+来自: [Self-Taught Agentic Long-Context Understanding, 第1页, Self-Taught Agentic Long-Context Understanding_chunk_000]</t>
+  </si>
+  <si>
+    <t>Agentic Reasoning是一个通过集成外部基于LLM的代理作为工具来增强推理的框架，允许LLM在推理过程中将特定任务委托给辅助代理。
+来自: [Agentic Reasoning: A Streamlined Framework for Enhancing LLM Reasoning with Agentic Tools, 第2页, Agentic Reasoning: A Streamlined Framework for Enhancing LLM Reasoning with Agentic Tools_chunk_003]</t>
+  </si>
+  <si>
+    <t>在Humanity's Last Exam上，Agentic Reasoning与DeepSeek-R1结合后准确率达到23.8%，相比基础模型DeepSeek-R1的9.4%提升了14.4个百分点。与OpenAI Deep Research的差距从原来的17.2%大幅缩小至仅2.8%。
+来自: [Agentic Reasoning: A Streamlined Framework for Enhancing LLM Reasoning with Agentic Tools, 第1页, Agentic Reasoning: A Streamlined Framework for Enhancing LLM Reasoning with Agentic Tools_chunk_002]</t>
+  </si>
+  <si>
+    <t>在GAIA基准测试中，Agentic Reasoning在Level 1、Level 2、Level 3上的得分分别为74.36、69.21、45.46，平均分66.13，在所有公开方法中达到最优。它在Level 1和Level 2上超越了OpenAI的Deep Research，在Level 3上将差距缩小至2.26%。
+来自: [Agentic Reasoning: A Streamlined Framework for Enhancing LLM Reasoning with Agentic Tools, 第5页, Agentic Reasoning: A Streamlined Framework for Enhancing LLM Reasoning with Agentic Tools_chunk_010]</t>
+  </si>
+  <si>
+    <t>AR-MCTS 的核心机制是主动检索（Active Retrieval）与蒙特卡洛树搜索（Monte Carlo Tree Search, MCTS）的结合；Agentic Reasoning 的核心机制是整合思维导图（Mind-Map）、网络搜索（web search）和代码执行（coding）。
+来自: [2025.acl-long.180_Progressive Multimodal Reasoning via Active Retrieval, 第1页, 2025.acl-long.180_Progressive Multimodal Reasoning via Active Retrieval_chunk_000]
+来自: [Agentic Reasoning: A Streamlined Framework for Enhancing LLM Reasoning with Agentic Tools, 第8页, Agentic Reasoning: A Streamlined Framework for Enhancing LLM Reasoning with Agentic Tools_chunk_017]</t>
+  </si>
+  <si>
+    <t>REAL-MM-RAG 基准测试旨在解决的四个关键属性是：(i) 多模态文档，(ii) 增强的难度，(iii) 真实 RAG 查询，以及 (iv) 准确的标注。
+来自: [REAL-MM-RAG:AReal-World Multi-Modal Retrieval Benchmark, 第1页, REAL-MM-RAG:AReal-World Multi-Modal Retrieval Benchmark_chunk_000]</t>
+  </si>
+  <si>
+    <t>ASTUTE RAG是一种新颖的RAG方法，旨在对不完美的检索增强具有弹性，同时在检索可靠时保留RAG的接地效果。它用于有效区分LLM内部知识与外部检索段落中的一致和冲突信息，评估其可靠性，并确保可信信息的正确整合，从而缓解知识冲突并提高响应的鲁棒性。
+来自: [ASTUTE RAG: Overcoming Imperfect Retrieval Augmentation and Knowledge Conflicts for Large Language Models, 第2页, ASTUTE RAG: Overcoming Imperfect Retrieval Augmentation and Knowledge Conflicts for Large Language Models_chunk_004]</t>
+  </si>
+  <si>
+    <t>knowledge consolidation过程包含三个主要步骤：识别跨段落的一致信息、检测一致信息组之间的冲突信息、过滤无关信息。
+来自: [ASTUTE RAG: Overcoming Imperfect Retrieval Augmentation and Knowledge Conflicts for Large Language Models, 第5页, ASTUTE RAG: Overcoming Imperfect Retrieval Augmentation and Knowledge Conflicts for Large Language Models_chunk_011]</t>
+  </si>
+  <si>
+    <t>L-CiteEval是一个开箱即用的评估套件，用于评估长上下文模型在长上下文理解任务中的生成质量和忠实度。
+来自: [L-CiteEval: A Suite for Evaluating Fidelity of Long-context Models, 第1页, L-CiteEval: A Suite for Evaluating Fidelity of Long-context Models_chunk_000]</t>
+  </si>
+  <si>
+    <t>LongBench v2基准测试包含503个多项选择题，上下文长度范围从8k到2M words。
+来自: [LongBench v2: Towards Deeper Understanding and Reasoning on Realistic Long-context Multitasks, 第1页, LongBench v2: Towards Deeper Understanding and Reasoning on Realistic Long-context Multitasks_chunk_002]</t>
+  </si>
+  <si>
+    <t>人类专家在15分钟时间限制下的准确率为53.7%。
+来自: [LongBench v2: Towards Deeper Understanding and Reasoning on Realistic Long-context Multitasks, 第1页, LongBench v2: Towards Deeper Understanding and Reasoning on Realistic Long-context Multitasks_chunk_000]</t>
+  </si>
+  <si>
+    <t>RHIO框架的三个主要组成部分是：不忠实数据增强（Unfaithful Data Augmentation）、忠实性感知微调（Faithfulness-Aware Tuning）和自我诱导解码（Self-Induced Decoding）。
+来自: [Improving Contextual Faithfulness of Large Language Models via Retrieval Heads-Induced Optimization, 第15页, Improving Contextual Faithfulness of Large Language Models via Retrieval Heads-Induced Optimization_chunk_030]</t>
+  </si>
+  <si>
+    <t>SYNQA 通过使用维基百科句子，提示大语言模型生成完全由这些句子支持的问题-答案对，从而合成归因训练数据。RHIO 则通过选择性遮蔽检索头来生成模拟模型内在错误的不忠实样本，并将这些样本用于联合训练，使模型能够区分忠实与不忠实的输出。
+在提升模型归因能力上，SYNQA 直接为归因任务合成高质量的问题-答案对及其支持句，用于微调小型归因模型，从而提升句子级归因的准确性和泛化能力。RHIO 并不直接生成归因数据，而是通过构造不忠实样本进行对比学习，增强大语言模型自身的上下文忠实度，间接改善模型在生成回答时对上下文的忠实归因能力。
+来自: [On Synthesizing Data for Context Attribution in Question Answering, 第2页, On Synthesizing Data for Context Attribution in Question Answering_chunk_003]
+来自: [Improving Contextual Faithfulness of Large Language Models via Retrieval Heads-Induced Optimization, 第1页, Improving Contextual Faithfulness of Large Language Models via Retrieval Heads-Induced Optimization_chunk_001]</t>
+  </si>
+  <si>
+    <t>作者发现，使用标准的短上下文指令数据集（standard, short-context instruction datasets）进行监督微调即可在长上下文任务上取得最佳性能，而长合成指令数据并未带来进一步提升。
+来自: [How to Train Long-Context Language Models (Effectively), 第1页, How to Train Long-Context Language Models (Effectively)_chunk_002]</t>
+  </si>
+  <si>
+    <t>LongRefiner 将推理过程拆分为离线和在线两个阶段：离线阶段预先对语料库中的文档执行层次化文档结构化任务，在线阶段仅需对用户查询进行分析并执行自适应精炼以生成最终输出。由于在线阶段只需处理数百个输入 token 并生成数十个输出 token，整体延迟仅为标准设置的约 25%。
+来自: [Hierarchical Document Refinement for Long-context Retrieval-augmented Generation, 第6页, Hierarchical Document Refinement for Long-context Retrieval-augmented Generation_chunk_013]</t>
+  </si>
+  <si>
+    <t>DRAG框架通过本地小模型对用户查询进行改写，剥离敏感信息后发送至云端大模型，云端仅返回证据和知识图谱，再由本地模型生成最终答案，从而避免用户隐私数据上传至云端。
+来自: [DRAG: Distilling RAG for SLMs from LLMs to Transfer Knowledge and Mitigate Hallucination via Evidence and Graph-based Distillation, 第5页, DRAG: Distilling RAG for SLMs from LLMs to Transfer Knowledge and Mitigate Hallucination via Evidence and Graph-based Distillation_chunk_010] 和 [DRAG: Distilling RAG for SLMs from LLMs to Transfer Knowledge and Mitigate Hallucination via Evidence and Graph-based Distillation, 第1页, DRAG: Distilling RAG for SLMs from LLMs to Transfer Knowledge and Mitigate Hallucination via Evidence and Graph-based Distillation_chunk_001]</t>
+  </si>
+  <si>
+    <t>SG-MCTS（自引导蒙特卡洛树搜索）将归因文本生成视为多步推理问题，每次迭代包含四个步骤：**选择**（用UCT算法选出最优节点）、**反思引导的扩展**（通过“思考-表达-引用”范式生成下一句，并利用LLM的自我反思能力实时批评和优化中间状态，避免错误路径）、**评估**（用进度奖励模型从生成进度和归因进度两方面计算奖励）以及**反向传播**（将奖励沿路径回传更新节点值）。
+来自: [Think&amp;Cite: Improving Attributed Text Generation with Self-Guided Tree Search and Progress Reward Modeling, 第3页, Think&amp;Cite: Improving Attributed Text Generation with Self-Guided Tree Search and Progress Reward Modeling_chunk_006]、[Think&amp;Cite: Improving Attributed Text Generation with Self-Guided Tree Search and Progress Reward Modeling, 第4页, Think&amp;Cite: Improving Attributed Text Generation with Self-Guided Tree Search and Progress Reward Modeling_chunk_008]、[Think&amp;Cite: Improving Attributed Text Generation with Self-Guided Tree Search and Progress Reward Modeling, 第7页, Think&amp;Cite: Improving Attributed Text Generation with Self-Guided Tree Search and Progress Reward Modeling_chunk_021]</t>
+  </si>
+  <si>
     <t>SETR 的段落选择提示引导的关键过程包含三个步骤：  
 1. 列举回答查询所需的关键信息需求；  
 2. 为每个信息需求找出包含相关信息的段落；  
 3. 选择一组段落，使其共同提供最全面、多样化的信息覆盖，以有效回答查询。  
-来自: [2025.acl-long.861_Shifting from Ranking to Set Selection for Retrieval Augmented Generation, 第3页, 2025.acl-long.861_Shifting from Ranking to Set Selection for Retrieval Augmented Generation_chunk_006]  
-来自: [2025.acl-long.861_Shifting from Ranking to Set Selection for Retrieval Augmented Generation, 第4页, 2025.acl-long.861_Shifting from Ranking to Set Selection for Retrieval Augmented Generation_chunk_008]</t>
-  </si>
-  <si>
-    <t>Meta-Bench基准测试中，α参数的最优范围是多少？这个参数的作用是什么？</t>
-  </si>
-  <si>
-    <t>α参数的最优范围在0.65到0.8之间。这个参数用于平衡工具描述和参数描述在工具检索中的权重。</t>
+来自: [Shifting from Ranking to Set Selection for Retrieval Augmented Generation, 第3页, Shifting from Ranking to Set Selection for Retrieval Augmented Generation_chunk_006]  
+来自: [Shifting from Ranking to Set Selection for Retrieval Augmented Generation, 第4页, Shifting from Ranking to Set Selection for Retrieval Augmented Generation_chunk_008]</t>
   </si>
   <si>
     <t>α参数的最优范围是 0.65 到 0.8。它的作用是在工具检索中平衡工具描述与参数描述的权重，从而优化检索命中率。
-来自: [2025.acl-long.1481_Meta-Tool, 第20页, 2025.acl-long.1481_Meta-Tool_chunk_033]</t>
-  </si>
-  <si>
-    <t>CypherBench 是如何从 RDF 图生成领域特定属性图的？</t>
-  </si>
-  <si>
-    <t>CypherBench 通过将 RDF 图转换为多个领域特定的属性图（domain-specific property graphs）来实现这一过程，并使用 Cypher 语言对其进行查询。</t>
+来自: [Meta-Tool: Unleash Open-World Function Calling Capabilities of General-Purpose Large Language Models, 第20页, Meta-Tool: Unleash Open-World Function Calling Capabilities of General-Purpose Large Language Models_chunk_033]</t>
   </si>
   <si>
     <t>CypherBench 通过将 RDF 图转换为多个领域特定的属性图，这些属性图作为底层 RDF 图的物化视图，通过执行 SPARQL 查询并聚合结果来生成，而非处理整个 RDF 转储；转换层同时负责数据类型转换和单位标准化，产出模式强制、严格类型化的数据。
-来自: [2025.acl-long.438_CypherBench, 第4页, 2025.acl-long.438_CypherBench_chunk_007]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ClinRaGen框架的三阶段理由蒸馏范式是什么？</t>
-  </si>
-  <si>
-    <t>ClinRaGen框架采用三阶段理由蒸馏范式：第一阶段从医疗笔记中蒸馏理由，让SLM发展对文本临床信息的基础理解；第二阶段引入知识增强注意力，将数值实验室测试与结构化医学知识对齐，蒸馏实验室测试为基础的理由；第三阶段完全整合文本和数值输入，使SLM能够生成临床连贯的多模态理由以支持疾病诊断。</t>
+来自: [CYPHERBENCH: Towards Precise Retrieval over Full-scale Modern Knowledge Graphs in the LLM Era, 第4页, CYPHERBENCH: Towards Precise Retrieval over Full-scale Modern Knowledge Graphs in the LLM Era_chunk_007]</t>
   </si>
   <si>
     <t>ClinRaGen的三阶段理由蒸馏范式是：第一阶段从医疗笔记中蒸馏理由，让SLM建立对文本临床信息的基础理解；第二阶段引入知识增强注意力，将数值实验室测试与结构化医学知识对齐，以蒸馏基于实验室测试的理由；第三阶段完全整合文本和数值输入，使SLM生成临床连贯的多模态理由来支持疾病诊断。
-来自: [2025.acl-long.540_Knowledge-Augmented Multimodal Clinical Rationale Generation for Disease Diagnosis with Small Language Models, 第4页, 2025.acl-long.540_Knowledge-Augmented Multimodal Clinical Rationale Generation for Disease Diagnosis with Small Language Models_chunk_008]</t>
-  </si>
-  <si>
-    <t>QAEncoder如何解决文档-查询差距问题？</t>
-  </si>
-  <si>
-    <t>QAEncoder采用了一种无需训练的方法来弥合文档与查询之间的差距。其核心机制包含两点：
-潜在查询期望估计： 在嵌入空间中估计潜在查询的期望值，将其作为文档嵌入的鲁棒替代表示，从而使文档表示在语义上更贴近查询空间。
-文档指纹附加： 为这些嵌入表示附加文档指纹，以有效区分不同文档的嵌入，避免仅依赖查询期望导致的文档辨识度丢失问题。</t>
+来自: [Knowledge-Augmented Multimodal Clinical Rationale Generation for Disease Diagnosis with Small Language Models, 第4页, Knowledge-Augmented Multimodal Clinical Rationale Generation for Disease Diagnosis with Small Language Models_chunk_008]</t>
   </si>
   <si>
     <t>QAEncoder采用查询中心的方法，通过为每个文档生成多样化的查询（如5W1H），并用蒙特卡洛方法估计这些潜在查询的聚类中心，以该聚类中心替代原始文档嵌入，从而在语义上对齐用户查询，弥合文档-查询差距。同时，为避免文档表示因趋同而丧失区分度，引入文档指纹策略，将文档独特身份重新注入表示中，实现高性能检索。
-来自: [2025.acl-long.217_QAEncoder, 第1页, 2025.acl-long.217_QAEncoder_chunk_003]  
-来自: [2025.acl-long.217_QAEncoder, 第2页, 2025.acl-long.217_QAEncoder_chunk_004]</t>
-  </si>
-  <si>
-    <t>在 HALOGEN 的文本简化任务中，如何验证模型生成的简化文本是否忠实于原文？</t>
-  </si>
-  <si>
-    <t>先用 GPT-3.5-turbo 将简化文本分解为独立的原子事实，再用 Llama-2-70B-chat 判断每个原子事实是否被原文蕴含。</t>
+来自: [QAEncoder: Towards Aligned Representation Learning in Question Answering Systems, 第1页, QAEncoder: Towards Aligned Representation Learning in Question Answering Systems_chunk_003]  
+来自: [QAEncoder: Towards Aligned Representation Learning in Question Answering Systems, 第2页, QAEncoder: Towards Aligned Representation Learning in Question Answering Systems_chunk_004]</t>
+  </si>
+  <si>
+    <t>QAEncoder侧重于优化检索阶段，核心痛点是文档与查询之间的语义差距（document-query gap），导致密集检索难以准确匹配用户查询。  
+On Synthesizing Data for Context Attribution in Question Answering侧重于优化归因阶段，核心痛点是缺乏大规模人工标注的归因数据，导致训练可靠的上下文归因模型成本高昂且泛化性不足。
+来自: [QAEncoder: Towards Aligned Representation Learning in Question Answering Systems, 第1页, QAEncoder: Towards Aligned Representation Learning in Question Answering Systems_chunk_003]  
+来自: [QAEncoder: Towards Aligned Representation Learning in Question Answering Systems, 第2页, QAEncoder: Towards Aligned Representation Learning in Question Answering Systems_chunk_004]  
+来自: [On Synthesizing Data for Context Attribution in Question Answering, 第9页, On Synthesizing Data for Context Attribution in Question Answering_chunk_024]  
+来自: [On Synthesizing Data for Context Attribution in Question Answering, 第9页, On Synthesizing Data for Context Attribution in Question Answering_chunk_023]</t>
   </si>
   <si>
     <t>在 HALOGEN 的文本简化任务中，验证过程与摘要任务相同：先用 GPT-3.5 将模型生成的简化文本分解为独立事实，再用 Llama-2-70B 对每个原子事实进行蕴含判断，以确认其是否忠实于原文。
-来自: [2025.acl-long.71_HALoGEN, 第3页, 2025.acl-long.71_HALoGEN_chunk_006]</t>
-  </si>
-  <si>
-    <t>在"CiteEval"论文中，GPT-4o和Llama-3-70B在Cited scenario和Full scenario下的表现有何差异？</t>
-  </si>
-  <si>
-    <t>实验结果类</t>
-  </si>
-  <si>
-    <t>在Cited scenario下，GPT-4o表现最佳，Llama-3-70B与GPT-4o-mini相当；在Full scenario下，Llama-3-70B超越GPT-4o，取得最佳性能。</t>
+来自: [HALOGEN :FantasticLLMHallucinations and Where to Find Them, 第3页, HALOGEN :FantasticLLMHallucinations and Where to Find Them_chunk_006]</t>
+  </si>
+  <si>
+    <t>在 HALoGEN 基准测试中，表现最好的 LLM（GPT-4）的幻觉率范围是 3% 到 86%，具体取决于任务。
+来自: [HALOGEN :FantasticLLMHallucinations and Where to Find Them, 第1页, HALOGEN :FantasticLLMHallucinations and Where to Find Them_chunk_001]</t>
   </si>
   <si>
     <t>在Cited scenario下，GPT-4o表现最佳，而Llama-3-70B与GPT-4o-mini性能相当；在Full scenario下，Llama-3-70B则优于GPT-4o，取得了最好的表现。
-来自: [2025.acl-long.1574_CiteEval, 第7页, 2025.acl-long.1574_CiteEval_chunk_018]</t>
-  </si>
-  <si>
-    <t>"FaithfulRAG"在FaithEval数据集上使用Mistral-7B作为backbone时的准确率是多少？相比最强基线提高了多少？</t>
-  </si>
-  <si>
-    <t>81.7%，比最强基线(KRE的73.2%)提高了8.5%。</t>
+来自: [CiteEval: Principle-Driven Citation Evaluation for Source Attribution, 第7页, CiteEval: Principle-Driven Citation Evaluation for Source Attribution_chunk_018]</t>
   </si>
   <si>
     <t>FaithfulRAG 在 FaithEval 数据集上使用 Mistral-7B 作为 backbone 时的准确率为 81.7%，相比最强基线（KRE 的 73.2%）提高了 8.5%。
-来自: [2025.acl-long.1062_FaithfulRAG, 第7页, 2025.acl-long.1062_FaithfulRAG_chunk_019]</t>
-  </si>
-  <si>
-    <t>RankCoT 相对于 vanilla RAG 模型的表现如何？这说明了什么？</t>
-  </si>
-  <si>
-    <t>RankCoT 相比 vanilla RAG 模型有 2.5% 的提升，表明它在提供更有意义的细化方面有效，有助于 LLM 更好地回答问题。</t>
-  </si>
-  <si>
-    <t>RankCoT 相比 vanilla RAG 模型在平均准确率上提升了约 2.5%，这表明 RankCoT 能够对检索到的知识进行更有效的精炼，生成保留关键信息的思维链，从而帮助大语言模型更准确地回答问题，同时避免了原始段落被重复输入带来的开销。
-来自: [2025.acl-long.629_RankCoT, 第6页, 2025.acl-long.629_RankCoT_chunk_018] 和 [2025.acl-long.629_RankCoT, 第12页, 2025.acl-long.629_RankCoT_chunk_026]</t>
-  </si>
-  <si>
-    <t>在 HALoGEN 基准测试中，表现最好的 LLM 生成事实的幻觉率范围是多少？</t>
-  </si>
-  <si>
-    <t>实验发现，即使是表现最好的 LLM，其生成事实的幻觉率也在 3% 到 86% 之间，具体数值取决于所属领域。</t>
-  </si>
-  <si>
-    <t>在 HALoGEN 基准测试中，表现最好的 LLM（GPT-4）的幻觉率范围是 3% 到 86%，具体取决于任务。
-来自: [2025.acl-long.71_HALoGEN, 第1页, 2025.acl-long.71_HALoGEN_chunk_001]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 在LongBench v2基准测试中，人类专家在15分钟时间限制下的准确率是多少？</t>
-  </si>
-  <si>
-    <t>人类专家在15分钟时间限制下的准确率为53.7%。</t>
-  </si>
-  <si>
-    <t>人类专家在15分钟时间限制下的准确率为53.7%。
-来自: [2025.acl-long.183_LongBench v2, 第1页, 2025.acl-long.183_LongBench v2_chunk_000]</t>
-  </si>
-  <si>
-    <t>AGENTSTAR方法在WebShop、ALFWorld和BabyAI任务上与GPT-4-Turbo相比有何优势？</t>
-  </si>
-  <si>
-    <t>AGENTSTAR 在这三个任务上的性能全面超越了 GPT-4-Turbo。其中在 WebShop 上的提升最为显著（远超 GPT-4-Turbo 61 个百分点），在 ALFWorld 和 BabyAI 上也分别实现了大幅领先（超过 GPT-4-Turbo 20.5 和 9.87 个百分点）。</t>
-  </si>
-  <si>
-    <t>AGENTSTAR 在 WebShop、ALFWorld 和 BabyAI 任务上分别比 GPT-4-Turbo 高出 61.00、20.50 和 9.87 分。
-来自: [2025.acl-long.1355_AgentGym, 第7页, 2025.acl-long.1355_AgentGym_chunk_020]</t>
-  </si>
-  <si>
-    <t>在Humanity's Last Exam数据集上，Agentic Reasoning与DeepSeek-R1结合的性能提升是多少？与OpenAI Deep Research的差距如何变化？</t>
-  </si>
-  <si>
-    <t>在Humanity's Last Exam数据集上，Agentic Reasoning与DeepSeek-R1结合达到了23.8%的准确率，比基础模型提升了14.4%，与专有的OpenAI Deep Research的差距缩小到仅2.8%。</t>
-  </si>
-  <si>
-    <t>在Humanity's Last Exam上，Agentic Reasoning与DeepSeek-R1结合后准确率达到23.8%，相比基础模型DeepSeek-R1的9.4%提升了14.4个百分点。与OpenAI Deep Research的差距从原来的17.2%大幅缩小至仅2.8%。
-来自: [2025.acl-long.1383_Agentic Reasoning, 第1页, 2025.acl-long.1383_Agentic Reasoning_chunk_002]</t>
-  </si>
-  <si>
-    <t>在GAIA基准测试中，Agentic Reasoning在不同级别任务上的表现如何？</t>
-  </si>
-  <si>
-    <t>在GAIA基准测试中，Agentic Reasoning在Level 1和Level 2任务上超越了OpenAI的Deep Research，在Level 3任务上将差距缩小到2.26%。</t>
-  </si>
-  <si>
-    <t>在GAIA基准测试中，Agentic Reasoning在Level 1、Level 2、Level 3上的得分分别为74.36、69.21、45.46，平均分66.13，在所有公开方法中达到最优。它在Level 1和Level 2上超越了OpenAI的Deep Research，在Level 3上将差距缩小至2.26%。
-来自: [2025.acl-long.1383_Agentic Reasoning, 第5页, 2025.acl-long.1383_Agentic Reasoning_chunk_010]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 在Asclepius医学基准测试中，人类医生与Med-MLLMs的表现对比如何？</t>
-  </si>
-  <si>
-    <t>在Asclepius基准测试中，人类医生在所有专业领域都超过了Med-MLLMs。即使是平均准确率为57.4%的初级医生也略微超过了表现最好的Med-MLLM GPT-4V（准确率为54.3%）。这表明尽管人工智能取得了进步，但在诊断精度方面人类专业知识与当前Med-MLLMs之间仍存在差距。</t>
-  </si>
-  <si>
-    <t>人类医生在所有专科的诊断准确性上均优于Med-MLLMs。例如，初级医生的平均准确率为57.4%，而表现最好的Med-MLLM GPT-4V仅为54.3%。GPT-4V与初级医生表现接近，有潜力辅助诊断，但所有Med-MLLMs的平均准确率均低于人类医生。
-来自: [2025.acl-long.1178_Asclepius, 第7页, 2025.acl-long.1178_Asclepius_chunk_016] 和 [2025.acl-long.1178_Asclepius, 第6页, 2025.acl-long.1178_Asclepius_chunk_013]</t>
-  </si>
-  <si>
-    <t>在LongDocURL基准测试中，GPT-4o的表现如何？其他开源模型呢？</t>
-  </si>
-  <si>
-    <t>在LongDocURL基准测试中，只有GPT-4o达到了及格标准，得分为64.5，表明该基准对当前模型提出了重大挑战。在开源模型中，只有Qwen2-VL（得分30.6）和LLaVA-OneVision（得分22.0和25.0）超过了20分的阈值，其他参数少于13B的模型都低于这个阈值。</t>
-  </si>
-  <si>
-    <t>在LongDocURL基准测试中，GPT-4o得分64.5，是最高分且唯一达到及格标准的模型。开源模型中，只有Qwen2-VL（得分30.6）和LLaVA-OneVision（得分22.0和25.0）得分超过20。
-来自: [2025.acl-long.57_LongDocURL, 第6页, 2025.acl-long.57_LongDocURL_chunk_013]</t>
-  </si>
-  <si>
-    <t>RAGEval 提出的自动评估指标与人工评估的一致性如何？</t>
-  </si>
-  <si>
-    <t>实验结果表明，RAGEval 的机器自动评估与人工评估在所有指标上均表现出高度一致性。两者之间的最终绝对差异仅为 1.67%。</t>
-  </si>
-  <si>
-    <t>RAGEval 使用 LLM 对提出的指标进行评分，与人工评估表现出高度一致性。
-来自: [2025.acl-long.418_RAGEval, 第1页, 2025.acl-long.418_RAGEval_chunk_000]</t>
-  </si>
-  <si>
-    <t>在利用大模型内部知识应对知识冲突时，《Astute RAG》与《FaithfulRAG》各自采用了什么核心机制/模块来提取或生成内部知识？</t>
-  </si>
-  <si>
-    <t>跨论文比较类</t>
-  </si>
-  <si>
-    <t>《Astute RAG》：采用自适应段落生成机制，通过提示大模型直接生成包含内部知识的段落，并允许模型自适应决定生成的段落数量。
-《FaithfulRAG》：采用自我事实挖掘 模块，通过外部化大模型对问题的理解，提取出细粒度的、事实级别的内部知识。</t>
+来自: [FaithfulRAG: Fact-Level Conflict Modeling for Context-Faithful Retrieval-Augmented Generation, 第7页, FaithfulRAG: Fact-Level Conflict Modeling for Context-Faithful Retrieval-Augmented Generation_chunk_019]</t>
   </si>
   <si>
     <t>《Astute RAG》采用“自适应内部知识生成”（adaptive generation of internal knowledge）机制，通过迭代方式从LLM内部动态生成关键信息。  
 《FaithfulRAG》则采用“Self-Fact Mining”模块，通过“Self-Knowledge Extraction → Self-Context Generation → Self-Fact Extraction”的三阶段层次化过程，将LLM的参数化知识外化为细粒度的事实表示。
-来自: [2025.acl-long.1476_Astute RAG, 第4页, 2025.acl-long.1476_Astute RAG_chunk_008]  
-来自: [2025.acl-long.1062_FaithfulRAG, 第4页, 2025.acl-long.1062_FaithfulRAG_chunk_010]</t>
-  </si>
-  <si>
-    <t>"UniRAG"和"FaithfulRAG"在处理查询理解方面的核心创新分别是什么？</t>
-  </si>
-  <si>
-    <t>UniRAG提出统一的查询理解框架，集成查询增强和查询编码两个阶段；FaithfulRAG通过自我事实挖掘和自思考模块，在事实级别识别并解决参数化知识与检索上下文之间的冲突，提高语义一致性。</t>
+来自: [ASTUTE RAG: Overcoming Imperfect Retrieval Augmentation and Knowledge Conflicts for Large Language Models, 第4页, ASTUTE RAG: Overcoming Imperfect Retrieval Augmentation and Knowledge Conflicts for Large Language Models_chunk_008]  
+来自: [FaithfulRAG: Fact-Level Conflict Modeling for Context-Faithful Retrieval-Augmented Generation, 第4页, FaithfulRAG: Fact-Level Conflict Modeling for Context-Faithful Retrieval-Augmented Generation_chunk_010]</t>
+  </si>
+  <si>
+    <t>RankCoT 相比 vanilla RAG 模型在平均准确率上提升了约 2.5%，这表明 RankCoT 能够对检索到的知识进行更有效的精炼，生成保留关键信息的思维链，从而帮助大语言模型更准确地回答问题，同时避免了原始段落被重复输入带来的开销。
+来自: [RankCoT: Refining Knowledge for Retrieval-Augmented Generation through Ranking Chain-of-Thoughts, 第6页, RankCoT: Refining Knowledge for Retrieval-Augmented Generation through Ranking Chain-of-Thoughts_chunk_018] 和 [RankCoT: Refining Knowledge for Retrieval-Augmented Generation through Ranking Chain-of-Thoughts, 第12页, RankCoT: Refining Knowledge for Retrieval-Augmented Generation through Ranking Chain-of-Thoughts_chunk_026]</t>
+  </si>
+  <si>
+    <t>AGENTSTAR 在 WebShop、ALFWorld 和 BabyAI 任务上分别比 GPT-4-Turbo 高出 61.00、20.50 和 9.87 分。
+来自: [AGENTGYM: Evaluating and Training Large Language Model-based Agents across Diverse Environments, 第7页, AGENTGYM: Evaluating and Training Large Language Model-based Agents across Diverse Environments_chunk_020]</t>
+  </si>
+  <si>
+    <t>LongBench v2 是一个静态评估基准，专注于测试大模型在长上下文（8k–2M词）下的深度理解与推理能力，覆盖单文档/多文档问答、长上下文学习、长对话历史、代码仓库和长结构化数据等现实多任务场景。  
+AGENTGYM 则是一个交互式框架，提供7个真实世界场景、14个环境和89个任务，支持多轮决策、实时反馈与自我改进，用于构建和训练能够跨环境执行任务的通用智能体。
+两者的核心区别在于：LongBench v2 用于一次性评估模型的长文本理解水平，不涉及交互或学习过程；AGENTGYM 用于在动态环境中训练和评估智能体的多步决策与自我进化能力。
+来自: [LongBench v2: Towards Deeper Understanding and Reasoning on Realistic Long-context Multitasks, 第1页, LongBench v2: Towards Deeper Understanding and Reasoning on Realistic Long-context Multitasks_chunk_002]  
+来自: [LongBench v2: Towards Deeper Understanding and Reasoning on Realistic Long-context Multitasks, 第1页, LongBench v2: Towards Deeper Understanding and Reasoning on Realistic Long-context Multitasks_chunk_000]  
+来自: [AGENTGYM: Evaluating and Training Large Language Model-based Agents across Diverse Environments, 第1页, AGENTGYM: Evaluating and Training Large Language Model-based Agents across Diverse Environments_chunk_001]</t>
+  </si>
+  <si>
+    <t>人类医生在所有专科的诊断准确性上均优于Med-MLLMs。例如，初级医生的平均准确率为57.4%，而表现最好的Med-MLLM GPT-4V仅为54.3%。GPT-4V与初级医生表现接近，有潜力辅助诊断，但所有Med-MLLMs的平均准确率均低于人类医生。
+来自: [Asclepius: A Spectrum Evaluation Benchmark for Medical Multi-Modal Large Language Models, 第7页, Asclepius: A Spectrum Evaluation Benchmark for Medical Multi-Modal Large Language Models_chunk_016] 和 [Asclepius: A Spectrum Evaluation Benchmark for Medical Multi-Modal Large Language Models, 第6页, Asclepius: A Spectrum Evaluation Benchmark for Medical Multi-Modal Large Language Models_chunk_013]</t>
+  </si>
+  <si>
+    <t>在LongDocURL基准测试中，GPT-4o得分64.5，是最高分且唯一达到及格标准的模型。开源模型中，只有Qwen2-VL（得分30.6）和LLaVA-OneVision（得分22.0和25.0）得分超过20。
+来自: [LongDocURL: a Comprehensive Multimodal Long Document Benchmark Integrating Understanding, Reasoning, and Locating, 第6页, LongDocURL: a Comprehensive Multimodal Long Document Benchmark Integrating Understanding, Reasoning, and Locating_chunk_013]</t>
+  </si>
+  <si>
+    <t>RAGEval 使用 LLM 对提出的指标进行评分，与人工评估表现出高度一致性。
+来自: [RAGEval: Scenario Specific RAG Evaluation Dataset Generation Framework, 第1页, RAGEval: Scenario Specific RAG Evaluation Dataset Generation Framework_chunk_000]</t>
   </si>
   <si>
     <t>UniRAG 的核心创新在于将查询增强与编码统一到一个解码器模型中，消除任务分离，并能够根据用户查询自适应选择最优增强策略（如查询改写、扩展、抽象）。FaithfulRAG 的核心创新则聚焦于生成阶段，在事实层面显式识别并解决模型参数知识与检索上下文之间的知识冲突，通过自事实对齐和自思考模块实现忠实生成。  
-来自: [2025.acl-long.693_UniRAG, 第1页, 2025.acl-long.693_UniRAG_chunk_000]  
-来自: [2025.acl-long.1062_FaithfulRAG, 第9页, 2025.acl-long.1062_FaithfulRAG_chunk_025]</t>
-  </si>
-  <si>
-    <t>比较MEMERAG和DragonBall两个基准的异同点，它们各自关注的评估维度是什么？</t>
-  </si>
-  <si>
-    <t>相同点：两者都是多语言RAG评估基准。不同点：MEMERAG专注于多语言端到端元评估，使用母语问题并由专家评估忠实度和相关性；DragonBall是一个多场景多语言RAG全能基准，涵盖金融、法律、医疗领域，包含6,711个问题，用于评估RAG系统在不同场景下的性能。</t>
+来自: [UniRAG: Unified Query Understanding Method for Retrieval Augmented Generation, 第1页, UniRAG: Unified Query Understanding Method for Retrieval Augmented Generation_chunk_000]  
+来自: [FaithfulRAG: Fact-Level Conflict Modeling for Context-Faithful Retrieval-Augmented Generation, 第9页, FaithfulRAG: Fact-Level Conflict Modeling for Context-Faithful Retrieval-Augmented Generation_chunk_025]</t>
   </si>
   <si>
     <t>MEMERAG和DragonBall都是用于RAG系统评估的基准，但存在明显差异。  
@@ -482,135 +606,16 @@
 - **构建方式**：MEMERAG基于原生语言的MIRACL数据集扩展，通过人工标注答案质量；DragonBall由RAGEval框架自动生成，通过迭代优化答案与关键点。  
 - **领域**：MEMERAG为通用领域（Wikipedia），DragonBall专注于金融、法律、医疗三个领域。  
 - **评估维度**：MEMERAG关注**Faithfulness（忠实度）**和**Relevance（相关性）**；DragonBall关注**Completeness（完整性）、Hallucination（幻觉）和Irrelevance（不相关性）**。
-来自: [2025.acl-long.1101_MEMERAG, 第3页, 2025.acl-long.1101_MEMERAG_chunk_007]  
-来自: [2025.acl-long.418_RAGEval, 第2页, 2025.acl-long.418_RAGEval_chunk_002]  
-来自: [2025.acl-long.418_RAGEval, 第4页, 2025.acl-long.418_RAGEval_chunk_008]</t>
-  </si>
-  <si>
-    <t>SYNQA 和 RHIO 分别通过什么方式生成训练数据？这两种数据生成策略在提升模型归因能力上有什么不同？</t>
-  </si>
-  <si>
-    <t>SYNQA：通过 LLM 生成式合成完全受上下文支持的 QA 对（正样本），用于微调小模型的归因能力。
-RHIO：通过选择性掩码检索头，让 LLM 自身生成模拟真实错误的不忠实样本（负样本），并与忠实样本进行联合训练。</t>
-  </si>
-  <si>
-    <t>SYNQA 通过使用维基百科句子，提示大语言模型生成完全由这些句子支持的问题-答案对，从而合成归因训练数据。RHIO 则通过选择性遮蔽检索头来生成模拟模型内在错误的不忠实样本，并将这些样本用于联合训练，使模型能够区分忠实与不忠实的输出。
-在提升模型归因能力上，SYNQA 直接为归因任务合成高质量的问题-答案对及其支持句，用于微调小型归因模型，从而提升句子级归因的准确性和泛化能力。RHIO 并不直接生成归因数据，而是通过构造不忠实样本进行对比学习，增强大语言模型自身的上下文忠实度，间接改善模型在生成回答时对上下文的忠实归因能力。
-来自: [2025.acl-long.828_On Synthesizing Data for Context Attribution in Question Answering, 第2页, 2025.acl-long.828_On Synthesizing Data for Context Attribution in Question Answering_chunk_003]
-来自: [2025.acl-long.826_Improving Contextual Faithfulness of Large Language Models via Retrieval Heads-Induced Optimization, 第1页, 2025.acl-long.826_Improving Contextual Faithfulness of Large Language Models via Retrieval Heads-Induced Optimization_chunk_001]</t>
-  </si>
-  <si>
-    <t>比较LongBench v2和AGENTGYM应用场景区别。</t>
-  </si>
-  <si>
-    <t>LongBench v2：专注于长上下文理解的多任务评估，包含503个多项选择题，上下文长度从8k到2M单词，涵盖6个主要任务类别，用于评估LLM在长文档理解和推理方面的能力
-AGENTGYM：专注于代理训练和工具使用的环境集合，包含11个不同的交互环境（如Minecraft、ScienceWorld、BabyAI等），用于训练和评估LLM代理在多样化任务中的能力</t>
-  </si>
-  <si>
-    <t>LongBench v2 是一个静态评估基准，专注于测试大模型在长上下文（8k–2M词）下的深度理解与推理能力，覆盖单文档/多文档问答、长上下文学习、长对话历史、代码仓库和长结构化数据等现实多任务场景。  
-AGENTGYM 则是一个交互式框架，提供7个真实世界场景、14个环境和89个任务，支持多轮决策、实时反馈与自我改进，用于构建和训练能够跨环境执行任务的通用智能体。
-两者的核心区别在于：LongBench v2 用于一次性评估模型的长文本理解水平，不涉及交互或学习过程；AGENTGYM 用于在动态环境中训练和评估智能体的多步决策与自我进化能力。
-来自: [2025.acl-long.183_LongBench v2, 第1页, 2025.acl-long.183_LongBench v2_chunk_002]  
-来自: [2025.acl-long.183_LongBench v2, 第1页, 2025.acl-long.183_LongBench v2_chunk_000]  
-来自: [2025.acl-long.1355_AgentGym, 第1页, 2025.acl-long.1355_AgentGym_chunk_001]</t>
-  </si>
-  <si>
-    <t>Agentic Reasoning 与 AR-MCTS 分别采用什么核心机制来提升复杂推理能力？</t>
-  </si>
-  <si>
-    <t>Agentic Reasoning：动态调用网页搜索、代码执行作为工具，并引入 Mind‑Map 知识图谱智能体作为结构化记忆，存储推理上下文并追踪逻辑关系。
-AR-MCTS：基于蒙特卡洛树搜索（MCTS），在扩展阶段集成主动检索（Active Retrieval） 机制，自动获取逐步推理的高质量标注，渐进式提升多模态大模型的推理能力。</t>
-  </si>
-  <si>
-    <t>AR-MCTS 的核心机制是主动检索（Active Retrieval）与蒙特卡洛树搜索（Monte Carlo Tree Search, MCTS）的结合；Agentic Reasoning 的核心机制是整合思维导图（Mind-Map）、网络搜索（web search）和代码执行（coding）。
-来自: [2025.acl-long.180_Progressive Multimodal Reasoning via Active Retrieval, 第1页, 2025.acl-long.180_Progressive Multimodal Reasoning via Active Retrieval_chunk_000]
-来自: [2025.acl-long.1383_Agentic Reasoning, 第8页, 2025.acl-long.1383_Agentic Reasoning_chunk_017]</t>
-  </si>
-  <si>
-    <t>MAIN‑RAG 与 RAG‑Critic 在提升 RAG 系统可靠性方面分别采用了什么核心方法？</t>
-  </si>
-  <si>
-    <t>MAIN‑RAG 采用多智能体协作过滤机制，通过三个 LLM 智能体（Predictor、Judge、Final‑Predictor）对检索文档进行相关性评分和排序，并利用自适应阈值动态过滤噪声文档，无需训练。
-RAG‑Critic 采用批评引导的智能体工作流，首先构建层次化 RAG 错误系统（3 级错误类型，含 4000+ 细粒度标签），然后训练轻量级错误批评模型进行自动错误诊断，最后通过规划智能体根据错误反馈定制并执行修正方案。</t>
-  </si>
-  <si>
-    <t>MAIN‑RAG 采用训练无关的多智能体协同过滤与自适应阈值机制，通过多个 LLM 智能体对检索文档进行评分和筛选，动态调整相关性阈值以降低噪声。RAG‑Critic 则构建数据驱动的层次化错误体系，训练错误批评模型，并利用批评引导的智能体工作流进行错误驱动的纠正，自动定制解决方案流程。
-来自: [2025.acl-long.131_MAIN-RAG, 第1页, 2025.acl-long.131_MAIN-RAG_chunk_004] 来自: [2025.acl-long.179_RAG-Critic, 第9页, 2025.acl-long.179_RAG-Critic_chunk_020]</t>
-  </si>
-  <si>
-    <t>在构建可靠的问答（QA）系统时，这QAEncoder与On Synthesizing Data for Context Attribution in Question Answering两篇论文分别侧重于优化系统工作流的哪个阶段？它们各自试图解决的核心痛点是什么？</t>
-  </si>
-  <si>
-    <t>《QAEncoder》侧重于“检索阶段”
-核心痛点：用户的自然语言查询与知识库中的文档之间存在语义和词汇上的鸿沟，导致检索模块无法精准召回相关文档。
-《On Synthesizing Data for Context Attribution... (SYNQA)》侧重于“生成后阶段”
-核心痛点：大语言模型在生成答案时容易产生幻觉，用户很难验证生成的答案是否真的基于提供的上下文，缺乏可解释性和事实依据。</t>
-  </si>
-  <si>
-    <t>QAEncoder侧重于优化检索阶段，核心痛点是文档与查询之间的语义差距（document-query gap），导致密集检索难以准确匹配用户查询。  
-On Synthesizing Data for Context Attribution in Question Answering侧重于优化归因阶段，核心痛点是缺乏大规模人工标注的归因数据，导致训练可靠的上下文归因模型成本高昂且泛化性不足。
-来自: [2025.acl-long.217_QAEncoder, 第1页, 2025.acl-long.217_QAEncoder_chunk_003]  
-来自: [2025.acl-long.217_QAEncoder, 第2页, 2025.acl-long.217_QAEncoder_chunk_004]  
-来自: [2025.acl-long.828_On Synthesizing Data for Context Attribution in Question Answering, 第9页, 2025.acl-long.828_On Synthesizing Data for Context Attribution in Question Answering_chunk_024]  
-来自: [2025.acl-long.828_On Synthesizing Data for Context Attribution in Question Answering, 第9页, 2025.acl-long.828_On Synthesizing Data for Context Attribution in Question Answering_chunk_023]</t>
-  </si>
-  <si>
-    <t>这10篇论文中哪一篇提出了名为"RAG-Guard"的安全防护框架？</t>
-  </si>
-  <si>
-    <t>不可回答类</t>
-  </si>
-  <si>
-    <t>无法回答。</t>
-  </si>
-  <si>
-    <t>根据已有信息，无法回答此问题。</t>
-  </si>
-  <si>
-    <t>"ProLong"模型在训练过程中使用了哪种具体的优化器来处理长序列训练的梯度问题？</t>
-  </si>
-  <si>
-    <t>SETR模型在训练时具体的训练时间是多少小时？</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> L-CiteEval基准中使用的NLI模型deberta-base-long-nli的准确率是多少？该模型在哪些具体数据集上进行了训练？</t>
-  </si>
-  <si>
-    <t>论文中是否提到了SYNQA方法在医疗领域的具体应用案例？</t>
-  </si>
-  <si>
-    <t>论文中是否提供了RHIO方法在实时应用场景中的延迟测试数据？</t>
-  </si>
-  <si>
-    <t>Agentic Reasoning框架中使用的Mind-Map agent的具体神经网络架构是什么？</t>
-  </si>
-  <si>
-    <t>在CypherBench基准测试中，每个问题模板具体包含多少个训练样本？</t>
-  </si>
-  <si>
-    <t>【总体平均值】</t>
-  </si>
-  <si>
-    <t>【定义类平均值】</t>
-  </si>
-  <si>
-    <t>【方法细节类平均值】</t>
-  </si>
-  <si>
-    <t>【实验结果类平均值】</t>
-  </si>
-  <si>
-    <t>【跨论文比较类平均值】</t>
-  </si>
-  <si>
-    <t>【不可回答类平均值】</t>
+来自: [MEMERAG:AMultilingual End-to-End Meta-Evaluation Benchmark for Retrieval Augmented Generation, 第3页, MEMERAG:AMultilingual End-to-End Meta-Evaluation Benchmark for Retrieval Augmented Generation_chunk_007]  
+来自: [RAGEval: Scenario Specific RAG Evaluation Dataset Generation Framework, 第2页, RAGEval: Scenario Specific RAG Evaluation Dataset Generation Framework_chunk_002]  
+来自: [RAGEval: Scenario Specific RAG Evaluation Dataset Generation Framework, 第4页, RAGEval: Scenario Specific RAG Evaluation Dataset Generation Framework_chunk_008]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -622,6 +627,7 @@
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -629,6 +635,14 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="161"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -673,7 +687,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -685,6 +699,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1047,18 +1064,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="252" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="D2" s="2" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
       <c r="E2" s="2">
         <v>1</v>
@@ -1093,104 +1110,104 @@
     </row>
     <row r="3" spans="1:15" ht="112" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1</v>
+      </c>
+      <c r="K3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2">
+        <v>1</v>
+      </c>
+      <c r="M3" s="2">
+        <v>0</v>
+      </c>
+      <c r="N3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="168" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1</v>
+      </c>
+      <c r="I4" s="4">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2">
+        <v>1</v>
+      </c>
+      <c r="K4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2">
+        <v>1</v>
+      </c>
+      <c r="M4" s="2">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="364" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0</v>
-      </c>
-      <c r="I3" s="4">
-        <v>1</v>
-      </c>
-      <c r="J3" s="2">
-        <v>1</v>
-      </c>
-      <c r="K3" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" s="2">
-        <v>1</v>
-      </c>
-      <c r="M3" s="2">
-        <v>0</v>
-      </c>
-      <c r="N3" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="2">
-        <v>1</v>
-      </c>
-      <c r="F4" s="2">
-        <v>1</v>
-      </c>
-      <c r="G4" s="2">
-        <v>1</v>
-      </c>
-      <c r="H4" s="2">
-        <v>1</v>
-      </c>
-      <c r="I4" s="4">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2">
-        <v>1</v>
-      </c>
-      <c r="K4" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" s="2">
-        <v>1</v>
-      </c>
-      <c r="M4" s="2">
-        <v>0</v>
-      </c>
-      <c r="N4" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>27</v>
+        <v>124</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
@@ -1225,16 +1242,16 @@
     </row>
     <row r="6" spans="1:15" ht="224" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>30</v>
+        <v>125</v>
       </c>
       <c r="E6" s="2">
         <v>1</v>
@@ -1267,18 +1284,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="224" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>33</v>
+        <v>126</v>
       </c>
       <c r="E7" s="2">
         <v>1</v>
@@ -1311,18 +1328,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="168" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>36</v>
+        <v>127</v>
       </c>
       <c r="E8" s="2">
         <v>1</v>
@@ -1355,18 +1372,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="168" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>39</v>
+        <v>131</v>
       </c>
       <c r="E9" s="2">
         <v>1</v>
@@ -1399,18 +1416,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="238" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>42</v>
+        <v>132</v>
       </c>
       <c r="E10" s="2">
         <v>1</v>
@@ -1443,18 +1460,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="238" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>45</v>
+        <v>134</v>
       </c>
       <c r="E11" s="2">
         <v>1</v>
@@ -1487,18 +1504,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="336" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="126" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>48</v>
+        <v>135</v>
       </c>
       <c r="E12" s="2">
         <v>1</v>
@@ -1531,18 +1548,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" ht="350" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>51</v>
+        <v>137</v>
       </c>
       <c r="E13" s="2">
         <v>1</v>
@@ -1575,18 +1592,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" ht="266" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>55</v>
+        <v>139</v>
       </c>
       <c r="E14" s="2">
         <v>1</v>
@@ -1601,7 +1618,7 @@
         <v>1</v>
       </c>
       <c r="I14" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="2">
         <v>1</v>
@@ -1619,18 +1636,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" ht="182" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>56</v>
+        <v>118</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="E15" s="2">
         <v>1</v>
@@ -1645,7 +1662,7 @@
         <v>1</v>
       </c>
       <c r="I15" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="2">
         <v>1</v>
@@ -1663,18 +1680,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="364" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>59</v>
+        <v>119</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>61</v>
+        <v>140</v>
       </c>
       <c r="E16" s="2">
         <v>0</v>
@@ -1707,18 +1724,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="252" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>64</v>
+        <v>141</v>
       </c>
       <c r="E17" s="2">
         <v>1</v>
@@ -1733,7 +1750,7 @@
         <v>1</v>
       </c>
       <c r="I17" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J17" s="2">
         <v>0.66700000000000004</v>
@@ -1753,16 +1770,16 @@
     </row>
     <row r="18" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>67</v>
+        <v>142</v>
       </c>
       <c r="E18" s="2">
         <v>1</v>
@@ -1797,16 +1814,16 @@
     </row>
     <row r="19" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>70</v>
+        <v>143</v>
       </c>
       <c r="E19" s="2">
         <v>1</v>
@@ -1821,7 +1838,7 @@
         <v>1</v>
       </c>
       <c r="I19" s="4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J19" s="2">
         <v>1</v>
@@ -1839,18 +1856,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="378" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="169" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>73</v>
+        <v>49</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>144</v>
       </c>
       <c r="E20" s="2">
         <v>1</v>
@@ -1883,18 +1900,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" ht="238" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>76</v>
+        <v>145</v>
       </c>
       <c r="E21" s="2">
         <v>1</v>
@@ -1929,16 +1946,16 @@
     </row>
     <row r="22" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="D22" s="2" t="s">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="E22" s="2">
         <v>1</v>
@@ -1973,16 +1990,16 @@
     </row>
     <row r="23" spans="1:14" ht="364" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="E23" s="2">
         <v>1</v>
@@ -2015,18 +2032,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="210" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>85</v>
+        <v>149</v>
       </c>
       <c r="E24" s="2">
         <v>1</v>
@@ -2059,18 +2076,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="168" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>89</v>
+        <v>151</v>
       </c>
       <c r="E25" s="2">
         <v>1</v>
@@ -2103,18 +2120,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="168" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>92</v>
+        <v>152</v>
       </c>
       <c r="E26" s="2">
         <v>1</v>
@@ -2147,18 +2164,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="294" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>95</v>
+        <v>154</v>
       </c>
       <c r="E27" s="2">
         <v>1</v>
@@ -2191,18 +2208,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="350" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="140" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="E28" s="2">
         <v>1</v>
@@ -2235,18 +2252,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="280" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="112" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>99</v>
+        <v>67</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>101</v>
+        <v>136</v>
       </c>
       <c r="E29" s="2">
         <v>1</v>
@@ -2279,18 +2296,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="406" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" ht="154" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>104</v>
+        <v>155</v>
       </c>
       <c r="E30" s="2">
         <v>1</v>
@@ -2323,18 +2340,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" ht="238" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="E31" s="2">
         <v>1</v>
@@ -2367,18 +2384,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" ht="238" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="E32" s="2">
         <v>1</v>
@@ -2411,18 +2428,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" ht="294" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>113</v>
+        <v>157</v>
       </c>
       <c r="E33" s="2">
         <v>1</v>
@@ -2455,18 +2472,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" ht="182" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>116</v>
+        <v>158</v>
       </c>
       <c r="E34" s="2">
         <v>1</v>
@@ -2499,18 +2516,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="294" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" ht="126" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>119</v>
+        <v>159</v>
       </c>
       <c r="E35" s="2">
         <v>1</v>
@@ -2545,16 +2562,16 @@
     </row>
     <row r="36" spans="1:15" ht="392" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>122</v>
+        <v>83</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="E36" s="2">
         <v>0</v>
@@ -2569,7 +2586,7 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="I36" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J36" s="2">
         <v>1</v>
@@ -2589,16 +2606,16 @@
     </row>
     <row r="37" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>125</v>
+        <v>85</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="E37" s="2">
         <v>1</v>
@@ -2633,16 +2650,16 @@
     </row>
     <row r="38" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>127</v>
+        <v>86</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>128</v>
+        <v>87</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>129</v>
+        <v>161</v>
       </c>
       <c r="E38" s="2">
         <v>1</v>
@@ -2657,7 +2674,7 @@
         <v>1</v>
       </c>
       <c r="I38" s="4">
-        <v>0.33329999999999999</v>
+        <v>0.66700000000000004</v>
       </c>
       <c r="J38" s="2">
         <v>0.66700000000000004</v>
@@ -2677,16 +2694,16 @@
     </row>
     <row r="39" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>130</v>
+        <v>88</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>131</v>
+        <v>89</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E39" s="2">
         <v>1</v>
@@ -2701,7 +2718,7 @@
         <v>1</v>
       </c>
       <c r="I39" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J39" s="2">
         <v>1</v>
@@ -2721,16 +2738,16 @@
     </row>
     <row r="40" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>133</v>
+        <v>90</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>134</v>
+        <v>91</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="E40" s="2">
         <v>1</v>
@@ -2763,18 +2780,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" ht="364" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>136</v>
+        <v>92</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>137</v>
+        <v>93</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="E41" s="2">
         <v>1</v>
@@ -2807,18 +2824,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" ht="322" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>139</v>
+        <v>94</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="E42" s="2">
         <v>0</v>
@@ -2833,7 +2850,7 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="I42" s="4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J42" s="2">
         <v>0.66700000000000004</v>
@@ -2853,16 +2870,16 @@
     </row>
     <row r="43" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>143</v>
+        <v>98</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E43" s="2">
         <v>0</v>
@@ -2877,7 +2894,7 @@
         <v>0</v>
       </c>
       <c r="I43" s="4">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="J43" s="2">
         <v>0.66700000000000004</v>
@@ -2895,18 +2912,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="112" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" ht="42" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>145</v>
+        <v>99</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>146</v>
+        <v>100</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="J44" s="2">
         <v>1</v>
@@ -2927,18 +2944,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="140" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" ht="56" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>149</v>
+        <v>103</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>146</v>
+        <v>100</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="J45" s="2">
         <v>1</v>
@@ -2959,18 +2976,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="84" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" ht="42" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>150</v>
+        <v>104</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>146</v>
+        <v>100</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="J46" s="2">
         <v>1</v>
@@ -2991,18 +3008,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="210" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" ht="84" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>151</v>
+        <v>105</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>146</v>
+        <v>100</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="J47" s="2">
         <v>1</v>
@@ -3023,18 +3040,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="98" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" ht="42" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>152</v>
+        <v>106</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>146</v>
+        <v>100</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="J48" s="2">
         <v>1</v>
@@ -3055,18 +3072,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="98" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" ht="42" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>153</v>
+        <v>107</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>146</v>
+        <v>100</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="J49" s="2">
         <v>1</v>
@@ -3087,18 +3104,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="126" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" ht="56" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>154</v>
+        <v>108</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>146</v>
+        <v>100</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="J50" s="2">
         <v>1</v>
@@ -3119,18 +3136,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="126" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" ht="42" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>155</v>
+        <v>109</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>146</v>
+        <v>100</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="J51" s="2">
         <v>1</v>
@@ -3151,9 +3168,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="28" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>156</v>
+        <v>110</v>
       </c>
       <c r="E53" s="2">
         <f>AVERAGEIFS(E2:E51,K2:K51,FALSE)</f>
@@ -3173,7 +3190,7 @@
       </c>
       <c r="I53" s="4">
         <f>AVERAGEIFS(I2:I51,K2:K51,FALSE)</f>
-        <v>0.86905476190476194</v>
+        <v>0.9305714285714286</v>
       </c>
       <c r="J53" s="2">
         <f>AVERAGE(J2:J51)</f>
@@ -3192,12 +3209,12 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="28" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>157</v>
+        <v>111</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E54" s="2">
         <f>AVERAGEIFS(E2:E51,B2:B51,"定义类",K2:K51,FALSE)</f>
@@ -3236,12 +3253,12 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="42" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" ht="28" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>158</v>
+        <v>112</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E55" s="2">
         <f>AVERAGEIFS(E2:E51,B2:B51,"方法细节类",K2:K51,FALSE)</f>
@@ -3261,7 +3278,7 @@
       </c>
       <c r="I55" s="4">
         <f>AVERAGEIFS(I2:I51,B2:B51,"方法细节类",K2:K51,FALSE)</f>
-        <v>0.69699999999999995</v>
+        <v>0.87881818181818183</v>
       </c>
       <c r="J55" s="2">
         <f>AVERAGEIF(B2:B51,"方法细节类",J2:J51)</f>
@@ -3280,12 +3297,12 @@
         <v>0.18181818181818182</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="42" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" ht="28" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="E56" s="2">
         <f>AVERAGEIFS(E2:E51,B2:B51,"实验结果类",K2:K51,FALSE)</f>
@@ -3324,12 +3341,12 @@
         <v>9.0909090909090912E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="42" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" ht="28" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>160</v>
+        <v>114</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="E57" s="2">
         <f>AVERAGEIFS(E2:E51,B2:B51,"跨论文比较类",K2:K51,FALSE)</f>
@@ -3349,7 +3366,7 @@
       </c>
       <c r="I57" s="4">
         <f>AVERAGEIFS(I2:I51,B2:B51,"跨论文比较类",K2:K51,FALSE)</f>
-        <v>0.72916249999999994</v>
+        <v>0.80212499999999998</v>
       </c>
       <c r="J57" s="2">
         <f>AVERAGEIF(B2:B51,"跨论文比较类",J2:J51)</f>
@@ -3368,12 +3385,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="42" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" ht="28" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>161</v>
+        <v>115</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>146</v>
+        <v>100</v>
       </c>
       <c r="E58" s="2" t="e">
         <f>AVERAGEIFS(E2:E51,B2:B51,"不可回答类",K2:K51,FALSE)</f>
@@ -3415,5 +3432,6 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/code/experiment/512chunk_BGE-M3-5topk_Y.xlsx
+++ b/code/experiment/512chunk_BGE-M3-5topk_Y.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rag_project\code\experiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9309F8E4-B59B-4152-BA6A-D8AD1D193924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE161240-2C9D-4C6E-A59C-DDA96804C38D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="13770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -192,9 +192,6 @@
     <t>α参数的最优范围在0.65到0.8之间。这个参数用于平衡工具描述和参数描述在工具检索中的权重。</t>
   </si>
   <si>
-    <t>CypherBench 是如何从 RDF 图生成领域特定属性图的？</t>
-  </si>
-  <si>
     <t>CypherBench 通过将 RDF 图转换为多个领域特定的属性图（domain-specific property graphs）来实现这一过程，并使用 Cypher 语言对其进行查询。</t>
   </si>
   <si>
@@ -609,6 +606,10 @@
 来自: [MEMERAG:AMultilingual End-to-End Meta-Evaluation Benchmark for Retrieval Augmented Generation, 第3页, MEMERAG:AMultilingual End-to-End Meta-Evaluation Benchmark for Retrieval Augmented Generation_chunk_007]  
 来自: [RAGEval: Scenario Specific RAG Evaluation Dataset Generation Framework, 第2页, RAGEval: Scenario Specific RAG Evaluation Dataset Generation Framework_chunk_002]  
 来自: [RAGEval: Scenario Specific RAG Evaluation Dataset Generation Framework, 第4页, RAGEval: Scenario Specific RAG Evaluation Dataset Generation Framework_chunk_008]</t>
+  </si>
+  <si>
+    <t>CypherBench 提出了什么核心方法来应对 RDF 查询的挑战？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1064,9 +1065,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="252" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="224" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
@@ -1075,7 +1076,7 @@
         <v>16</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E2" s="2">
         <v>1</v>
@@ -1108,7 +1109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="112" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="210" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
@@ -1119,7 +1120,7 @@
         <v>18</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E3" s="2">
         <v>0</v>
@@ -1152,9 +1153,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="168" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="252" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>15</v>
@@ -1163,7 +1164,7 @@
         <v>19</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E4" s="2">
         <v>1</v>
@@ -1196,7 +1197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="364" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>20</v>
       </c>
@@ -1207,7 +1208,7 @@
         <v>21</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
@@ -1251,7 +1252,7 @@
         <v>23</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E6" s="2">
         <v>1</v>
@@ -1284,7 +1285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="224" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="210" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>24</v>
       </c>
@@ -1295,7 +1296,7 @@
         <v>25</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E7" s="2">
         <v>1</v>
@@ -1328,7 +1329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="168" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="252" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>26</v>
       </c>
@@ -1339,7 +1340,7 @@
         <v>27</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E8" s="2">
         <v>1</v>
@@ -1372,7 +1373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="168" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="210" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>28</v>
       </c>
@@ -1383,7 +1384,7 @@
         <v>29</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E9" s="2">
         <v>1</v>
@@ -1416,7 +1417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="238" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="350" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>30</v>
       </c>
@@ -1427,7 +1428,7 @@
         <v>31</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E10" s="2">
         <v>1</v>
@@ -1471,7 +1472,7 @@
         <v>33</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E11" s="2">
         <v>1</v>
@@ -1504,7 +1505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="126" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="238" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>34</v>
       </c>
@@ -1515,7 +1516,7 @@
         <v>35</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E12" s="2">
         <v>1</v>
@@ -1548,7 +1549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="350" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" ht="322" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>36</v>
       </c>
@@ -1559,7 +1560,7 @@
         <v>37</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E13" s="2">
         <v>1</v>
@@ -1592,9 +1593,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="266" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" ht="238" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>38</v>
@@ -1603,7 +1604,7 @@
         <v>39</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E14" s="2">
         <v>1</v>
@@ -1636,9 +1637,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="182" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" ht="266" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>38</v>
@@ -1647,7 +1648,7 @@
         <v>40</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E15" s="2">
         <v>1</v>
@@ -1680,9 +1681,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="364" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="336" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>38</v>
@@ -1691,7 +1692,7 @@
         <v>41</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E16" s="2">
         <v>0</v>
@@ -1724,7 +1725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="252" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>42</v>
       </c>
@@ -1735,7 +1736,7 @@
         <v>43</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E17" s="2">
         <v>1</v>
@@ -1779,7 +1780,7 @@
         <v>45</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E18" s="2">
         <v>1</v>
@@ -1823,7 +1824,7 @@
         <v>47</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E19" s="2">
         <v>1</v>
@@ -1856,7 +1857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="169" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="280" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>48</v>
       </c>
@@ -1867,7 +1868,7 @@
         <v>49</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E20" s="2">
         <v>1</v>
@@ -1900,18 +1901,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="238" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" ht="336" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>50</v>
+        <v>161</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E21" s="2">
         <v>1</v>
@@ -1944,18 +1945,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="378" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E22" s="2">
         <v>1</v>
@@ -1988,18 +1989,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="364" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E23" s="2">
         <v>1</v>
@@ -2032,18 +2033,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="210" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="252" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E24" s="2">
         <v>1</v>
@@ -2076,18 +2077,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="168" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="238" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="D25" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E25" s="2">
         <v>1</v>
@@ -2120,194 +2121,194 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="168" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="252" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E26" s="2">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>1</v>
+      </c>
+      <c r="G26" s="2">
+        <v>1</v>
+      </c>
+      <c r="H26" s="2">
+        <v>1</v>
+      </c>
+      <c r="I26" s="4">
+        <v>1</v>
+      </c>
+      <c r="J26" s="2">
+        <v>1</v>
+      </c>
+      <c r="K26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" s="2">
+        <v>1</v>
+      </c>
+      <c r="M26" s="2">
+        <v>0</v>
+      </c>
+      <c r="N26" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E26" s="2">
-        <v>1</v>
-      </c>
-      <c r="F26" s="2">
-        <v>1</v>
-      </c>
-      <c r="G26" s="2">
-        <v>1</v>
-      </c>
-      <c r="H26" s="2">
-        <v>1</v>
-      </c>
-      <c r="I26" s="4">
-        <v>1</v>
-      </c>
-      <c r="J26" s="2">
-        <v>1</v>
-      </c>
-      <c r="K26" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L26" s="2">
-        <v>1</v>
-      </c>
-      <c r="M26" s="2">
-        <v>0</v>
-      </c>
-      <c r="N26" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="294" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
+      <c r="B27" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E27" s="2">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>1</v>
+      </c>
+      <c r="G27" s="2">
+        <v>1</v>
+      </c>
+      <c r="H27" s="2">
+        <v>1</v>
+      </c>
+      <c r="I27" s="4">
+        <v>1</v>
+      </c>
+      <c r="J27" s="2">
+        <v>1</v>
+      </c>
+      <c r="K27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" s="2">
+        <v>1</v>
+      </c>
+      <c r="M27" s="2">
+        <v>0</v>
+      </c>
+      <c r="N27" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="182" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="B28" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E28" s="2">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>1</v>
+      </c>
+      <c r="G28" s="2">
+        <v>1</v>
+      </c>
+      <c r="H28" s="2">
+        <v>1</v>
+      </c>
+      <c r="I28" s="4">
+        <v>1</v>
+      </c>
+      <c r="J28" s="2">
+        <v>1</v>
+      </c>
+      <c r="K28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" s="2">
+        <v>1</v>
+      </c>
+      <c r="M28" s="2">
+        <v>0</v>
+      </c>
+      <c r="N28" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="224" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E29" s="2">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>1</v>
+      </c>
+      <c r="G29" s="2">
+        <v>1</v>
+      </c>
+      <c r="H29" s="2">
+        <v>1</v>
+      </c>
+      <c r="I29" s="4">
+        <v>1</v>
+      </c>
+      <c r="J29" s="2">
+        <v>1</v>
+      </c>
+      <c r="K29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" s="2">
+        <v>1</v>
+      </c>
+      <c r="M29" s="2">
+        <v>0</v>
+      </c>
+      <c r="N29" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="238" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="E27" s="2">
-        <v>1</v>
-      </c>
-      <c r="F27" s="2">
-        <v>1</v>
-      </c>
-      <c r="G27" s="2">
-        <v>1</v>
-      </c>
-      <c r="H27" s="2">
-        <v>1</v>
-      </c>
-      <c r="I27" s="4">
-        <v>1</v>
-      </c>
-      <c r="J27" s="2">
-        <v>1</v>
-      </c>
-      <c r="K27" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L27" s="2">
-        <v>1</v>
-      </c>
-      <c r="M27" s="2">
-        <v>0</v>
-      </c>
-      <c r="N27" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" ht="140" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E28" s="2">
-        <v>1</v>
-      </c>
-      <c r="F28" s="2">
-        <v>1</v>
-      </c>
-      <c r="G28" s="2">
-        <v>1</v>
-      </c>
-      <c r="H28" s="2">
-        <v>1</v>
-      </c>
-      <c r="I28" s="4">
-        <v>1</v>
-      </c>
-      <c r="J28" s="2">
-        <v>1</v>
-      </c>
-      <c r="K28" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L28" s="2">
-        <v>1</v>
-      </c>
-      <c r="M28" s="2">
-        <v>0</v>
-      </c>
-      <c r="N28" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" ht="112" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E29" s="2">
-        <v>1</v>
-      </c>
-      <c r="F29" s="2">
-        <v>1</v>
-      </c>
-      <c r="G29" s="2">
-        <v>1</v>
-      </c>
-      <c r="H29" s="2">
-        <v>1</v>
-      </c>
-      <c r="I29" s="4">
-        <v>1</v>
-      </c>
-      <c r="J29" s="2">
-        <v>1</v>
-      </c>
-      <c r="K29" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L29" s="2">
-        <v>1</v>
-      </c>
-      <c r="M29" s="2">
-        <v>0</v>
-      </c>
-      <c r="N29" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="154" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="E30" s="2">
         <v>1</v>
@@ -2340,18 +2341,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="238" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" ht="322" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="D31" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E31" s="2">
         <v>1</v>
@@ -2384,18 +2385,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="238" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" ht="322" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="D32" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E32" s="2">
         <v>1</v>
@@ -2428,18 +2429,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="294" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="D33" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E33" s="2">
         <v>1</v>
@@ -2472,18 +2473,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="182" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" ht="336" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="D34" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E34" s="2">
         <v>1</v>
@@ -2516,18 +2517,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="126" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" ht="182" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="D35" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E35" s="2">
         <v>1</v>
@@ -2560,18 +2561,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="392" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="D36" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E36" s="2">
         <v>0</v>
@@ -2606,16 +2607,16 @@
     </row>
     <row r="37" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="D37" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E37" s="2">
         <v>1</v>
@@ -2650,16 +2651,16 @@
     </row>
     <row r="38" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="D38" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E38" s="2">
         <v>1</v>
@@ -2694,16 +2695,16 @@
     </row>
     <row r="39" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>89</v>
-      </c>
       <c r="D39" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E39" s="2">
         <v>1</v>
@@ -2738,16 +2739,16 @@
     </row>
     <row r="40" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="D40" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E40" s="2">
         <v>1</v>
@@ -2780,18 +2781,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="364" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="D41" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E41" s="2">
         <v>1</v>
@@ -2826,16 +2827,16 @@
     </row>
     <row r="42" spans="1:15" ht="322" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C42" s="2" t="s">
+      <c r="D42" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="E42" s="2">
         <v>0</v>
@@ -2870,16 +2871,16 @@
     </row>
     <row r="43" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="D43" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E43" s="2">
         <v>0</v>
@@ -2914,16 +2915,16 @@
     </row>
     <row r="44" spans="1:15" ht="42" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="C44" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="D44" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="J44" s="2">
         <v>1</v>
@@ -2946,16 +2947,16 @@
     </row>
     <row r="45" spans="1:15" ht="56" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="D45" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="J45" s="2">
         <v>1</v>
@@ -2978,16 +2979,16 @@
     </row>
     <row r="46" spans="1:15" ht="42" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="D46" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="J46" s="2">
         <v>1</v>
@@ -3010,16 +3011,16 @@
     </row>
     <row r="47" spans="1:15" ht="84" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B47" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="D47" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="J47" s="2">
         <v>1</v>
@@ -3042,16 +3043,16 @@
     </row>
     <row r="48" spans="1:15" ht="42" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B48" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="D48" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="J48" s="2">
         <v>1</v>
@@ -3074,16 +3075,16 @@
     </row>
     <row r="49" spans="1:15" ht="42" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B49" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="D49" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="J49" s="2">
         <v>1</v>
@@ -3106,16 +3107,16 @@
     </row>
     <row r="50" spans="1:15" ht="56" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B50" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="D50" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="J50" s="2">
         <v>1</v>
@@ -3138,16 +3139,16 @@
     </row>
     <row r="51" spans="1:15" ht="42" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B51" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="D51" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="J51" s="2">
         <v>1</v>
@@ -3170,7 +3171,7 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E53" s="2">
         <f>AVERAGEIFS(E2:E51,K2:K51,FALSE)</f>
@@ -3211,7 +3212,7 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>15</v>
@@ -3255,7 +3256,7 @@
     </row>
     <row r="55" spans="1:15" ht="28" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>38</v>
@@ -3299,10 +3300,10 @@
     </row>
     <row r="56" spans="1:15" ht="28" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E56" s="2">
         <f>AVERAGEIFS(E2:E51,B2:B51,"实验结果类",K2:K51,FALSE)</f>
@@ -3343,10 +3344,10 @@
     </row>
     <row r="57" spans="1:15" ht="28" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E57" s="2">
         <f>AVERAGEIFS(E2:E51,B2:B51,"跨论文比较类",K2:K51,FALSE)</f>
@@ -3387,10 +3388,10 @@
     </row>
     <row r="58" spans="1:15" ht="28" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E58" s="2" t="e">
         <f>AVERAGEIFS(E2:E51,B2:B51,"不可回答类",K2:K51,FALSE)</f>
